--- a/data/wordpress-security-production.xlsx
+++ b/data/wordpress-security-production.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作管理表" sheetId="1" r:id="Rf65080718dbe4d4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成共通プロンプト" sheetId="2" r:id="Rc09e385d43e74ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成プロンプト一覧" sheetId="3" r:id="R9c2a17e0779e4d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWデータ" sheetId="4" r:id="Rcea84f5d65c842a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執筆・QAルール" sheetId="5" r:id="Rcd860203111c4701"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進捗サマリー" sheetId="6" r:id="R8109b07c91dc4b37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作管理表" sheetId="1" r:id="R8724f6af9bda4a80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成共通プロンプト" sheetId="2" r:id="R74dbcf76961d4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成プロンプト一覧" sheetId="3" r:id="R5a1ab38c7bfe41be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWデータ" sheetId="4" r:id="Rd649f53adb424f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執筆・QAルール" sheetId="5" r:id="Rfac6666001c940e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進捗サマリー" sheetId="6" r:id="Re4ee56c5817f4a20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -123,7 +123,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -133,7 +133,7 @@
         <x:color rgb="FF1D4ED8"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -143,7 +143,7 @@
         <x:color rgb="FF0369A1"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0F2FE"/>
         </x:patternFill>
       </x:fill>
@@ -153,7 +153,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -480,7 +480,7 @@
         <x:v>wordpress セキュリティ チェック</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>wordpress セキュリティ チェック</x:v>
+        <x:v>更新状況、設定不備、不要プラグイン、管理者権限、外部診断</x:v>
       </x:c>
       <x:c r="G2" s="16" t="n">
         <x:v>20</x:v>
@@ -498,28 +498,28 @@
         <x:v>単独／CV最優先</x:v>
       </x:c>
       <x:c r="L2" s="16" t="str">
-        <x:v>WordPressのセキュリティチェック方法｜無料で脆弱性と設定不備を可視化する</x:v>
+        <x:v>WordPressセキュリティチェック｜無料診断の手順</x:v>
       </x:c>
       <x:c r="M2" s="16" t="str">
         <x:v>wordpress-security-check</x:v>
       </x:c>
       <x:c r="N2" s="16" t="str">
-        <x:v>WordPressのセキュリティチェック方法をテーマに、無料で脆弱性と設定不備を可視化するための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ チェックで確認する更新状況、管理者設定、不要プラグインを整理します。無料診断と管理画面確認の違い、結果を高・中・低の優先度に分ける方法まで分かります。確認する順番も一覧で把握できます。</x:v>
       </x:c>
       <x:c r="O2" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P2" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q2" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R2" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S2" s="14" t="str">
-        <x:v>WordPress、セキュリティ、脆弱性対策</x:v>
+        <x:v>設定監査、基本対策、脆弱性管理</x:v>
       </x:c>
       <x:c r="T2" s="14" t="str">
         <x:v>01,23,03</x:v>
@@ -534,7 +534,7 @@
         <x:v>006.png</x:v>
       </x:c>
       <x:c r="X2" s="14" t="str">
-        <x:v>WordPressのセキュリティチェック方法｜無料で脆弱性と設定不備を可視化する</x:v>
+        <x:v>WordPressセキュリティチェック｜無料診断の手順</x:v>
       </x:c>
       <x:c r="Y2" s="16" t="str">
         <x:v>未着手</x:v>
@@ -548,15 +548,15 @@
       <x:c r="AB2" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC2" s="16" t="str"/>
-      <x:c r="AD2" s="16" t="str"/>
-      <x:c r="AE2" s="16" t="str"/>
-      <x:c r="AF2" s="16" t="str"/>
-      <x:c r="AG2" s="16" t="str"/>
-      <x:c r="AH2" s="16" t="str"/>
-      <x:c r="AI2" s="16" t="str"/>
-      <x:c r="AJ2" s="14" t="str"/>
-      <x:c r="AK2" s="14" t="str"/>
+      <x:c r="AC2" s="16"/>
+      <x:c r="AD2" s="16"/>
+      <x:c r="AE2" s="16"/>
+      <x:c r="AF2" s="16"/>
+      <x:c r="AG2" s="16"/>
+      <x:c r="AH2" s="16"/>
+      <x:c r="AI2" s="16"/>
+      <x:c r="AJ2" s="14"/>
+      <x:c r="AK2" s="14"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="16" t="n">
@@ -571,8 +571,10 @@
       <x:c r="D3" s="16" t="str">
         <x:v>強</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str"/>
-      <x:c r="F3" s="14" t="str"/>
+      <x:c r="E3" s="14"/>
+      <x:c r="F3" s="14" t="str">
+        <x:v>診断結果、優先順位、設定不備、改善手順、再診断</x:v>
+      </x:c>
       <x:c r="G3" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -589,28 +591,28 @@
         <x:v>CV専用</x:v>
       </x:c>
       <x:c r="L3" s="16" t="str">
-        <x:v>CyberNote Security Checkerの使い方｜診断結果の読み方と対処の優先順位</x:v>
+        <x:v>CyberNote Security Checker｜診断結果</x:v>
       </x:c>
       <x:c r="M3" s="16" t="str">
         <x:v>cybernote-security-checker-guide</x:v>
       </x:c>
       <x:c r="N3" s="16" t="str">
-        <x:v>CyberNote Security Checkerの使い方をテーマに、診断結果の読み方と対処の優先順位ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>CyberNote Security Checkerの診断項目、結果画面の読み方、対応順序をまとめます。警告をそのまま直すのではなく、影響と作業難度から優先順位を決め、再診断まで進められる案内です。日常点検へつなげられます。</x:v>
       </x:c>
       <x:c r="O3" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P3" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q3" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R3" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S3" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>設定監査、セキュリティプラグイン、基本対策</x:v>
       </x:c>
       <x:c r="T3" s="14" t="str">
         <x:v>01,06,15</x:v>
@@ -625,7 +627,7 @@
         <x:v>023.png</x:v>
       </x:c>
       <x:c r="X3" s="14" t="str">
-        <x:v>CyberNote Security Checkerの使い方｜診断結果の読み方と対処の優先順位</x:v>
+        <x:v>CyberNote Security Checker｜診断結果</x:v>
       </x:c>
       <x:c r="Y3" s="16" t="str">
         <x:v>未着手</x:v>
@@ -639,15 +641,15 @@
       <x:c r="AB3" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC3" s="16" t="str"/>
-      <x:c r="AD3" s="16" t="str"/>
-      <x:c r="AE3" s="16" t="str"/>
-      <x:c r="AF3" s="16" t="str"/>
-      <x:c r="AG3" s="16" t="str"/>
-      <x:c r="AH3" s="16" t="str"/>
-      <x:c r="AI3" s="16" t="str"/>
-      <x:c r="AJ3" s="14" t="str"/>
-      <x:c r="AK3" s="14" t="str"/>
+      <x:c r="AC3" s="16"/>
+      <x:c r="AD3" s="16"/>
+      <x:c r="AE3" s="16"/>
+      <x:c r="AF3" s="16"/>
+      <x:c r="AG3" s="16"/>
+      <x:c r="AH3" s="16"/>
+      <x:c r="AI3" s="16"/>
+      <x:c r="AJ3" s="14"/>
+      <x:c r="AK3" s="14"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="16" t="n">
@@ -666,7 +668,7 @@
         <x:v>wordpress セキュリティ プラグイン 複数</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>wordpress セキュリティ プラグイン 複数</x:v>
+        <x:v>競合、併用、干渉、ログインできない、ロックアウト、WAF</x:v>
       </x:c>
       <x:c r="G4" s="16" t="n">
         <x:v>10</x:v>
@@ -684,28 +686,28 @@
         <x:v>単独／CV最重要</x:v>
       </x:c>
       <x:c r="L4" s="16" t="str">
-        <x:v>WordPressセキュリティプラグインは複数入れていい？競合する組み合わせと安全な併用</x:v>
+        <x:v>WordPressセキュリティプラグイン複数利用の注意点</x:v>
       </x:c>
       <x:c r="M4" s="16" t="str">
         <x:v>multiple-wordpress-security-plugins</x:v>
       </x:c>
       <x:c r="N4" s="16" t="str">
-        <x:v>WordPressセキュリティプラグインは複数入れていい？競合する組み合わせと安全な併用について、必要な設定、判断基準、注意点を実務目線で解説します。WordPress運用者が迷いやすい点を整理し、次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ プラグイン 複数利用で起きる競合、二重遮断、ログイン不能を整理します。WAF、二要素認証、回数制限の役割を分け、残す機能と停止する機能を判断できます。解除や復旧の手順も確認できます。</x:v>
       </x:c>
       <x:c r="O4" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P4" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q4" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R4" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S4" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、ログイン防御、WAF・サーバー</x:v>
       </x:c>
       <x:c r="T4" s="14" t="str">
         <x:v>01,23,11,13</x:v>
@@ -720,7 +722,7 @@
         <x:v>015.png</x:v>
       </x:c>
       <x:c r="X4" s="14" t="str">
-        <x:v>WordPressセキュリティプラグインは複数入れていい？競合する組み合わせと安全な併用</x:v>
+        <x:v>WordPressセキュリティプラグイン複数利用の注意点</x:v>
       </x:c>
       <x:c r="Y4" s="16" t="str">
         <x:v>未着手</x:v>
@@ -734,15 +736,15 @@
       <x:c r="AB4" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC4" s="16" t="str"/>
-      <x:c r="AD4" s="16" t="str"/>
-      <x:c r="AE4" s="16" t="str"/>
-      <x:c r="AF4" s="16" t="str"/>
-      <x:c r="AG4" s="16" t="str"/>
-      <x:c r="AH4" s="16" t="str"/>
-      <x:c r="AI4" s="16" t="str"/>
-      <x:c r="AJ4" s="14" t="str"/>
-      <x:c r="AK4" s="14" t="str"/>
+      <x:c r="AC4" s="16"/>
+      <x:c r="AD4" s="16"/>
+      <x:c r="AE4" s="16"/>
+      <x:c r="AF4" s="16"/>
+      <x:c r="AG4" s="16"/>
+      <x:c r="AH4" s="16"/>
+      <x:c r="AI4" s="16"/>
+      <x:c r="AJ4" s="14"/>
+      <x:c r="AK4" s="14"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="16" t="n">
@@ -761,7 +763,7 @@
         <x:v>wordpress セキュリティ プラグイン 無料</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>wordpress セキュリティ プラグイン 無料</x:v>
+        <x:v>無料版、ファイアウォール、マルウェアスキャン、二要素認証、更新頻度、サポート</x:v>
       </x:c>
       <x:c r="G5" s="16" t="n">
         <x:v>20</x:v>
@@ -779,28 +781,28 @@
         <x:v>単独／CV</x:v>
       </x:c>
       <x:c r="L5" s="16" t="str">
-        <x:v>無料で使えるWordPressセキュリティプラグイン8選｜機能の境界線を明示する</x:v>
+        <x:v>WordPressセキュリティプラグイン無料版8選</x:v>
       </x:c>
       <x:c r="M5" s="16" t="str">
         <x:v>free-wordpress-security-plugins</x:v>
       </x:c>
       <x:c r="N5" s="16" t="str">
-        <x:v>無料で使えるWordPressセキュリティプラグイン8選をテーマに、機能の境界線を明示するための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ プラグイン 無料版8製品を、WAF、スキャン、二要素認証、ログ機能で比較します。無料で使える範囲と有料版が必要になる条件を見極め、導入候補を絞れます。選定時の比較軸が明確になります。</x:v>
       </x:c>
       <x:c r="O5" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>7,000字</x:v>
       </x:c>
       <x:c r="P5" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="Q5" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="R5" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S5" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、基本対策、ログイン防御</x:v>
       </x:c>
       <x:c r="T5" s="14" t="str">
         <x:v>01,23,11,13</x:v>
@@ -815,7 +817,7 @@
         <x:v>012.png</x:v>
       </x:c>
       <x:c r="X5" s="14" t="str">
-        <x:v>無料で使えるWordPressセキュリティプラグイン8選｜機能の境界線を明示する</x:v>
+        <x:v>WordPressセキュリティプラグイン無料版8選</x:v>
       </x:c>
       <x:c r="Y5" s="16" t="str">
         <x:v>未着手</x:v>
@@ -829,15 +831,15 @@
       <x:c r="AB5" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC5" s="16" t="str"/>
-      <x:c r="AD5" s="16" t="str"/>
-      <x:c r="AE5" s="16" t="str"/>
-      <x:c r="AF5" s="16" t="str"/>
-      <x:c r="AG5" s="16" t="str"/>
-      <x:c r="AH5" s="16" t="str"/>
-      <x:c r="AI5" s="16" t="str"/>
-      <x:c r="AJ5" s="14" t="str"/>
-      <x:c r="AK5" s="14" t="str"/>
+      <x:c r="AC5" s="16"/>
+      <x:c r="AD5" s="16"/>
+      <x:c r="AE5" s="16"/>
+      <x:c r="AF5" s="16"/>
+      <x:c r="AG5" s="16"/>
+      <x:c r="AH5" s="16"/>
+      <x:c r="AI5" s="16"/>
+      <x:c r="AJ5" s="14"/>
+      <x:c r="AK5" s="14"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="16" t="n">
@@ -856,7 +858,7 @@
         <x:v>wordpress セキュリティ 脆弱性</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>wordpress セキュリティ 脆弱性</x:v>
+        <x:v>プラグイン脆弱性、テーマ脆弱性、JVN、WPScan、CVE、アップデート</x:v>
       </x:c>
       <x:c r="G6" s="16" t="n">
         <x:v>30</x:v>
@@ -874,28 +876,28 @@
         <x:v>単独／CV</x:v>
       </x:c>
       <x:c r="L6" s="16" t="str">
-        <x:v>WordPressの脆弱性とは｜コア・テーマ・プラグインの実態と確認方法</x:v>
+        <x:v>WordPressの脆弱性｜確認方法と対処手順</x:v>
       </x:c>
       <x:c r="M6" s="16" t="str">
         <x:v>wordpress-vulnerabilities</x:v>
       </x:c>
       <x:c r="N6" s="16" t="str">
-        <x:v>WordPressの脆弱性とはをテーマに、コア・テーマ・プラグインの実態と確認方法ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 脆弱性をコア、テーマ、プラグインの3層に分けて確認します。JVN・CVE・WPScanで影響バージョンを照合し、更新・停止・代替のどれを選ぶか判断できます。緊急対応の要否も見分けられます。</x:v>
       </x:c>
       <x:c r="O6" s="16" t="str">
-        <x:v>10,000字</x:v>
+        <x:v>7,500字</x:v>
       </x:c>
       <x:c r="P6" s="16" t="n">
-        <x:v>9700</x:v>
+        <x:v>6375</x:v>
       </x:c>
       <x:c r="Q6" s="16" t="n">
-        <x:v>10300</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="R6" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S6" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>脆弱性管理、アップデート運用、セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="T6" s="14" t="str">
         <x:v>01,23,26,27,29</x:v>
@@ -910,7 +912,7 @@
         <x:v>024.png</x:v>
       </x:c>
       <x:c r="X6" s="14" t="str">
-        <x:v>WordPressの脆弱性とは｜コア・テーマ・プラグインの実態と確認方法</x:v>
+        <x:v>WordPressの脆弱性｜確認方法と対処手順</x:v>
       </x:c>
       <x:c r="Y6" s="16" t="str">
         <x:v>未着手</x:v>
@@ -924,15 +926,15 @@
       <x:c r="AB6" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC6" s="16" t="str"/>
-      <x:c r="AD6" s="16" t="str"/>
-      <x:c r="AE6" s="16" t="str"/>
-      <x:c r="AF6" s="16" t="str"/>
-      <x:c r="AG6" s="16" t="str"/>
-      <x:c r="AH6" s="16" t="str"/>
-      <x:c r="AI6" s="16" t="str"/>
-      <x:c r="AJ6" s="14" t="str"/>
-      <x:c r="AK6" s="14" t="str"/>
+      <x:c r="AC6" s="16"/>
+      <x:c r="AD6" s="16"/>
+      <x:c r="AE6" s="16"/>
+      <x:c r="AF6" s="16"/>
+      <x:c r="AG6" s="16"/>
+      <x:c r="AH6" s="16"/>
+      <x:c r="AI6" s="16"/>
+      <x:c r="AJ6" s="14"/>
+      <x:c r="AK6" s="14"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="16" t="n">
@@ -947,9 +949,9 @@
       <x:c r="D7" s="16" t="str">
         <x:v>強</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="str"/>
+      <x:c r="E7" s="14"/>
       <x:c r="F7" s="14" t="str">
-        <x:v>wordpress セキュリティ 情報</x:v>
+        <x:v>セキュリティアドバイザリ、影響バージョン、CVSS、悪用情報、更新通知</x:v>
       </x:c>
       <x:c r="G7" s="16" t="n">
         <x:v>0</x:v>
@@ -967,28 +969,28 @@
         <x:v>見送り→#29は残す（CV導線として重要。KW期待値はゼロ）</x:v>
       </x:c>
       <x:c r="L7" s="16" t="str">
-        <x:v>WordPressの脆弱性情報を収集する方法｜JVN・CVE・WPScanの使い分け</x:v>
+        <x:v>WordPress脆弱性情報｜JVN・CVE・WPScan</x:v>
       </x:c>
       <x:c r="M7" s="16" t="str">
         <x:v>wordpress-vulnerability-information</x:v>
       </x:c>
       <x:c r="N7" s="16" t="str">
-        <x:v>WordPressの脆弱性情報を収集する方法をテーマに、JVN・CVE・WPScanの使い分けための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>JVN、CVE、WPScan、WordPress公式をどの順番で確認するかを整理します。製品名、影響バージョン、修正版、悪用情報を照合し、自分のサイトに関係する脆弱性だけを選別できます。日々の情報収集を効率化できます。</x:v>
       </x:c>
       <x:c r="O7" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P7" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q7" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R7" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S7" s="14" t="str">
-        <x:v>WordPress、セキュリティ、脆弱性対策</x:v>
+        <x:v>脆弱性管理、アップデート運用、設定監査</x:v>
       </x:c>
       <x:c r="T7" s="14" t="str">
         <x:v>01,23,24</x:v>
@@ -1003,7 +1005,7 @@
         <x:v>029.png</x:v>
       </x:c>
       <x:c r="X7" s="14" t="str">
-        <x:v>WordPressの脆弱性情報を収集する方法｜JVN・CVE・WPScanの使い分け</x:v>
+        <x:v>WordPress脆弱性情報｜JVN・CVE・WPScan</x:v>
       </x:c>
       <x:c r="Y7" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1017,15 +1019,15 @@
       <x:c r="AB7" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC7" s="16" t="str"/>
-      <x:c r="AD7" s="16" t="str"/>
-      <x:c r="AE7" s="16" t="str"/>
-      <x:c r="AF7" s="16" t="str"/>
-      <x:c r="AG7" s="16" t="str"/>
-      <x:c r="AH7" s="16" t="str"/>
-      <x:c r="AI7" s="16" t="str"/>
-      <x:c r="AJ7" s="14" t="str"/>
-      <x:c r="AK7" s="14" t="str"/>
+      <x:c r="AC7" s="16"/>
+      <x:c r="AD7" s="16"/>
+      <x:c r="AE7" s="16"/>
+      <x:c r="AF7" s="16"/>
+      <x:c r="AG7" s="16"/>
+      <x:c r="AH7" s="16"/>
+      <x:c r="AI7" s="16"/>
+      <x:c r="AJ7" s="14"/>
+      <x:c r="AK7" s="14"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="n">
@@ -1044,7 +1046,7 @@
         <x:v>wordpress セキュリティ パッチ</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>wordpress セキュリティ パッチ</x:v>
+        <x:v>ステージング環境、バックアップ、互換性確認、ロールバック、メンテナンス</x:v>
       </x:c>
       <x:c r="G8" s="16" t="n">
         <x:v>10</x:v>
@@ -1062,28 +1064,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L8" s="16" t="str">
-        <x:v>WordPressのセキュリティパッチ適用手順｜検証環境と切り戻しの実務</x:v>
+        <x:v>WordPressセキュリティパッチの適用手順</x:v>
       </x:c>
       <x:c r="M8" s="16" t="str">
         <x:v>wordpress-security-patch</x:v>
       </x:c>
       <x:c r="N8" s="16" t="str">
-        <x:v>WordPressのセキュリティパッチ適用手順をテーマに、検証環境と切り戻しの実務ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ パッチを本番へ直接適用せず、バックアップ、検証環境、互換性確認、切り戻しの順で進めます。更新失敗時の判断点も押さえ、安全に公開を再開できます。メンテナンス計画にも落とし込めます。</x:v>
       </x:c>
       <x:c r="O8" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P8" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q8" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R8" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S8" s="14" t="str">
-        <x:v>WordPress、セキュリティ、脆弱性対策</x:v>
+        <x:v>アップデート運用、バックアップ、脆弱性管理</x:v>
       </x:c>
       <x:c r="T8" s="14" t="str">
         <x:v>01,23,24,29</x:v>
@@ -1098,7 +1100,7 @@
         <x:v>026.png</x:v>
       </x:c>
       <x:c r="X8" s="14" t="str">
-        <x:v>WordPressのセキュリティパッチ適用手順｜検証環境と切り戻しの実務</x:v>
+        <x:v>WordPressセキュリティパッチの適用手順</x:v>
       </x:c>
       <x:c r="Y8" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1112,15 +1114,15 @@
       <x:c r="AB8" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC8" s="16" t="str"/>
-      <x:c r="AD8" s="16" t="str"/>
-      <x:c r="AE8" s="16" t="str"/>
-      <x:c r="AF8" s="16" t="str"/>
-      <x:c r="AG8" s="16" t="str"/>
-      <x:c r="AH8" s="16" t="str"/>
-      <x:c r="AI8" s="16" t="str"/>
-      <x:c r="AJ8" s="14" t="str"/>
-      <x:c r="AK8" s="14" t="str"/>
+      <x:c r="AC8" s="16"/>
+      <x:c r="AD8" s="16"/>
+      <x:c r="AE8" s="16"/>
+      <x:c r="AF8" s="16"/>
+      <x:c r="AG8" s="16"/>
+      <x:c r="AH8" s="16"/>
+      <x:c r="AI8" s="16"/>
+      <x:c r="AJ8" s="14"/>
+      <x:c r="AK8" s="14"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="n">
@@ -1139,7 +1141,7 @@
         <x:v>wordpress セキュリティアップデート</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>wordpress セキュリティアップデート</x:v>
+        <x:v>自動更新、メジャー更新、マイナー更新、互換性、更新通知、切り戻し</x:v>
       </x:c>
       <x:c r="G9" s="16" t="n">
         <x:v>20</x:v>
@@ -1157,28 +1159,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L9" s="16" t="str">
-        <x:v>WordPressの自動更新は有効にすべきか｜メジャー・マイナーの判断基準</x:v>
+        <x:v>WordPressセキュリティアップデートの判断基準</x:v>
       </x:c>
       <x:c r="M9" s="16" t="str">
         <x:v>wordpress-auto-update-security</x:v>
       </x:c>
       <x:c r="N9" s="16" t="str">
-        <x:v>WordPressの自動更新は有効にすべきかをテーマに、メジャー・マイナーの判断基準ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティアップデートを自動化する範囲を、コアのメジャー・マイナー、テーマ、プラグイン別に整理します。緊急度と互換性リスクから、自動更新と手動検証を選べます。更新ポリシーの作成にも使えます。</x:v>
       </x:c>
       <x:c r="O9" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P9" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q9" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R9" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S9" s="14" t="str">
-        <x:v>WordPress、セキュリティ、脆弱性対策</x:v>
+        <x:v>アップデート運用、脆弱性管理、バックアップ</x:v>
       </x:c>
       <x:c r="T9" s="14" t="str">
         <x:v>01,23,24,29</x:v>
@@ -1193,7 +1195,7 @@
         <x:v>027.png</x:v>
       </x:c>
       <x:c r="X9" s="14" t="str">
-        <x:v>WordPressの自動更新は有効にすべきか｜メジャー・マイナーの判断基準</x:v>
+        <x:v>WordPressセキュリティアップデートの判断基準</x:v>
       </x:c>
       <x:c r="Y9" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1207,15 +1209,15 @@
       <x:c r="AB9" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC9" s="16" t="str"/>
-      <x:c r="AD9" s="16" t="str"/>
-      <x:c r="AE9" s="16" t="str"/>
-      <x:c r="AF9" s="16" t="str"/>
-      <x:c r="AG9" s="16" t="str"/>
-      <x:c r="AH9" s="16" t="str"/>
-      <x:c r="AI9" s="16" t="str"/>
-      <x:c r="AJ9" s="14" t="str"/>
-      <x:c r="AK9" s="14" t="str"/>
+      <x:c r="AC9" s="16"/>
+      <x:c r="AD9" s="16"/>
+      <x:c r="AE9" s="16"/>
+      <x:c r="AF9" s="16"/>
+      <x:c r="AG9" s="16"/>
+      <x:c r="AH9" s="16"/>
+      <x:c r="AI9" s="16"/>
+      <x:c r="AJ9" s="14"/>
+      <x:c r="AK9" s="14"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="16" t="n">
@@ -1234,7 +1236,7 @@
         <x:v>wordpress セキュリティ設定</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>wordpress セキュリティ設定</x:v>
+        <x:v>管理者権限、ファイル編集、XML-RPC、デバッグモード、SSL、不要アカウント</x:v>
       </x:c>
       <x:c r="G10" s="16" t="n">
         <x:v>70</x:v>
@@ -1252,28 +1254,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L10" s="16" t="str">
-        <x:v>WordPressのセキュリティ設定チェックリスト｜必ず確認する20項目</x:v>
+        <x:v>WordPressセキュリティ設定20項目チェック</x:v>
       </x:c>
       <x:c r="M10" s="16" t="str">
         <x:v>wordpress-security-settings-checklist</x:v>
       </x:c>
       <x:c r="N10" s="16" t="str">
-        <x:v>WordPressのセキュリティ設定チェックリストをテーマに、必ず確認する20項目ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ設定を20項目に分け、管理者権限、SSL、XML-RPC、ファイル編集、デバッグ表示を確認します。未設定の箇所を一覧化し、影響の大きい順に修正できます。設定画面ごとの確認先も把握できます。</x:v>
       </x:c>
       <x:c r="O10" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>7,500字</x:v>
       </x:c>
       <x:c r="P10" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>6375</x:v>
       </x:c>
       <x:c r="Q10" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="R10" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S10" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>設定監査、基本対策、ログイン防御</x:v>
       </x:c>
       <x:c r="T10" s="14" t="str">
         <x:v>01,23,06</x:v>
@@ -1288,7 +1290,7 @@
         <x:v>003.png</x:v>
       </x:c>
       <x:c r="X10" s="14" t="str">
-        <x:v>WordPressのセキュリティ設定チェックリスト｜必ず確認する20項目</x:v>
+        <x:v>WordPressセキュリティ設定20項目チェック</x:v>
       </x:c>
       <x:c r="Y10" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1302,15 +1304,15 @@
       <x:c r="AB10" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC10" s="16" t="str"/>
-      <x:c r="AD10" s="16" t="str"/>
-      <x:c r="AE10" s="16" t="str"/>
-      <x:c r="AF10" s="16" t="str"/>
-      <x:c r="AG10" s="16" t="str"/>
-      <x:c r="AH10" s="16" t="str"/>
-      <x:c r="AI10" s="16" t="str"/>
-      <x:c r="AJ10" s="14" t="str"/>
-      <x:c r="AK10" s="14" t="str"/>
+      <x:c r="AC10" s="16"/>
+      <x:c r="AD10" s="16"/>
+      <x:c r="AE10" s="16"/>
+      <x:c r="AF10" s="16"/>
+      <x:c r="AG10" s="16"/>
+      <x:c r="AH10" s="16"/>
+      <x:c r="AI10" s="16"/>
+      <x:c r="AJ10" s="14"/>
+      <x:c r="AK10" s="14"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="n">
@@ -1329,7 +1331,7 @@
         <x:v>wordpress 初期設定 セキュリティ</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>wordpress 初期設定 セキュリティ</x:v>
+        <x:v>管理者ユーザー、パーマリンク、SSL化、更新設定、バックアップ、不要テーマ</x:v>
       </x:c>
       <x:c r="G11" s="16" t="n">
         <x:v>10</x:v>
@@ -1347,28 +1349,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L11" s="16" t="str">
-        <x:v>WordPress初期設定でやるべきセキュリティ設定｜公開前の最終確認</x:v>
+        <x:v>WordPress初期設定のセキュリティ確認項目</x:v>
       </x:c>
       <x:c r="M11" s="16" t="str">
         <x:v>wordpress-initial-security-settings</x:v>
       </x:c>
       <x:c r="N11" s="16" t="str">
-        <x:v>WordPress初期設定でやるべきセキュリティ設定をテーマに、公開前の最終確認ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress 初期設定 セキュリティで公開前に確認したい管理者名、SSL、自動更新、バックアップ、不要テーマをまとめます。公開後に戻しにくい設定を先に済ませ、初日から安全に運用できます。公開前チェックにもそのまま使えます。</x:v>
       </x:c>
       <x:c r="O11" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P11" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q11" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R11" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S11" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、バックアップ</x:v>
       </x:c>
       <x:c r="T11" s="14" t="str">
         <x:v>01,23,03,06</x:v>
@@ -1383,7 +1385,7 @@
         <x:v>005.png</x:v>
       </x:c>
       <x:c r="X11" s="14" t="str">
-        <x:v>WordPress初期設定でやるべきセキュリティ設定｜公開前の最終確認</x:v>
+        <x:v>WordPress初期設定のセキュリティ確認項目</x:v>
       </x:c>
       <x:c r="Y11" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1397,15 +1399,15 @@
       <x:c r="AB11" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC11" s="16" t="str"/>
-      <x:c r="AD11" s="16" t="str"/>
-      <x:c r="AE11" s="16" t="str"/>
-      <x:c r="AF11" s="16" t="str"/>
-      <x:c r="AG11" s="16" t="str"/>
-      <x:c r="AH11" s="16" t="str"/>
-      <x:c r="AI11" s="16" t="str"/>
-      <x:c r="AJ11" s="14" t="str"/>
-      <x:c r="AK11" s="14" t="str"/>
+      <x:c r="AC11" s="16"/>
+      <x:c r="AD11" s="16"/>
+      <x:c r="AE11" s="16"/>
+      <x:c r="AF11" s="16"/>
+      <x:c r="AG11" s="16"/>
+      <x:c r="AH11" s="16"/>
+      <x:c r="AI11" s="16"/>
+      <x:c r="AJ11" s="14"/>
+      <x:c r="AK11" s="14"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="16" t="n">
@@ -1424,7 +1426,7 @@
         <x:v>wordpress セキュリティ 大全</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>wordpress セキュリティ 大全</x:v>
+        <x:v>セキュリティ監査、運用ルール、権限管理、脆弱性管理、バックアップ、復旧</x:v>
       </x:c>
       <x:c r="G12" s="16" t="n">
         <x:v>10</x:v>
@@ -1442,28 +1444,28 @@
         <x:v>単独／GEO引用の本命</x:v>
       </x:c>
       <x:c r="L12" s="16" t="str">
-        <x:v>WordPressセキュリティ大全｜運用者のための全項目チェックリスト</x:v>
+        <x:v>WordPressセキュリティ大全｜運用チェックリスト</x:v>
       </x:c>
       <x:c r="M12" s="16" t="str">
         <x:v>wordpress-security-complete-checklist</x:v>
       </x:c>
       <x:c r="N12" s="16" t="str">
-        <x:v>WordPressセキュリティ大全をテーマに、運用者のための全項目チェックリストための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 大全として、予防、検知、対応、復旧の4段階を一つの監査表にまとめます。担当者、確認頻度、証跡まで決め、抜けのない運用体制を設計できます。月次点検の土台としても利用できます。</x:v>
       </x:c>
       <x:c r="O12" s="16" t="str">
-        <x:v>14,000字</x:v>
+        <x:v>10,000字</x:v>
       </x:c>
       <x:c r="P12" s="16" t="n">
-        <x:v>13580</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="Q12" s="16" t="n">
-        <x:v>14420</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="R12" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S12" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、インシデント対応</x:v>
       </x:c>
       <x:c r="T12" s="14" t="str">
         <x:v>01,23,03,06</x:v>
@@ -1478,7 +1480,7 @@
         <x:v>008.png</x:v>
       </x:c>
       <x:c r="X12" s="14" t="str">
-        <x:v>WordPressセキュリティ大全｜運用者のための全項目チェックリスト</x:v>
+        <x:v>WordPressセキュリティ大全｜運用チェックリスト</x:v>
       </x:c>
       <x:c r="Y12" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1492,15 +1494,15 @@
       <x:c r="AB12" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC12" s="16" t="str"/>
-      <x:c r="AD12" s="16" t="str"/>
-      <x:c r="AE12" s="16" t="str"/>
-      <x:c r="AF12" s="16" t="str"/>
-      <x:c r="AG12" s="16" t="str"/>
-      <x:c r="AH12" s="16" t="str"/>
-      <x:c r="AI12" s="16" t="str"/>
-      <x:c r="AJ12" s="14" t="str"/>
-      <x:c r="AK12" s="14" t="str"/>
+      <x:c r="AC12" s="16"/>
+      <x:c r="AD12" s="16"/>
+      <x:c r="AE12" s="16"/>
+      <x:c r="AF12" s="16"/>
+      <x:c r="AG12" s="16"/>
+      <x:c r="AH12" s="16"/>
+      <x:c r="AI12" s="16"/>
+      <x:c r="AJ12" s="14"/>
+      <x:c r="AK12" s="14"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="n">
@@ -1515,9 +1517,9 @@
       <x:c r="D13" s="16" t="str">
         <x:v>強</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="str"/>
+      <x:c r="E13" s="14"/>
       <x:c r="F13" s="14" t="str">
-        <x:v>wordpress ユーザー 名 セキュリティ</x:v>
+        <x:v>author slug、ユーザー列挙、REST API、表示名、ログインID、リダイレクト</x:v>
       </x:c>
       <x:c r="G13" s="16" t="n">
         <x:v>0</x:v>
@@ -1535,28 +1537,28 @@
         <x:v>見送り→#39は残すがKW期待値ゼロ。CV補助として作成</x:v>
       </x:c>
       <x:c r="L13" s="16" t="str">
-        <x:v>WordPressのユーザー名が漏れる仕組みと対策｜author slugとREST API</x:v>
+        <x:v>WordPressユーザー名漏えい｜author・API</x:v>
       </x:c>
       <x:c r="M13" s="16" t="str">
         <x:v>wordpress-username-exposure</x:v>
       </x:c>
       <x:c r="N13" s="16" t="str">
-        <x:v>WordPressのユーザー名が漏れる仕組みと対策をテーマに、author slugとREST APIための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>authorページ、REST API、投稿者表示からWordPressのユーザー名が見える経路を確認します。ログインIDと表示名の分離、公開範囲の調整を行い、攻撃者に渡す情報を減らせます。列挙できる状態の確認方法も示します。</x:v>
       </x:c>
       <x:c r="O13" s="16" t="str">
-        <x:v>6,000字</x:v>
+        <x:v>5,000字</x:v>
       </x:c>
       <x:c r="P13" s="16" t="n">
-        <x:v>5820</x:v>
+        <x:v>4250</x:v>
       </x:c>
       <x:c r="Q13" s="16" t="n">
-        <x:v>6180</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="R13" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; ログインと管理画面</x:v>
       </x:c>
       <x:c r="S13" s="14" t="str">
-        <x:v>WordPress、セキュリティ、ログイン対策</x:v>
+        <x:v>ログイン防御、API・開発、設定監査</x:v>
       </x:c>
       <x:c r="T13" s="14" t="str">
         <x:v>01,23,03,06</x:v>
@@ -1571,7 +1573,7 @@
         <x:v>039.png</x:v>
       </x:c>
       <x:c r="X13" s="14" t="str">
-        <x:v>WordPressのユーザー名が漏れる仕組みと対策｜author slugとREST API</x:v>
+        <x:v>WordPressユーザー名漏えい｜author・API</x:v>
       </x:c>
       <x:c r="Y13" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1585,15 +1587,15 @@
       <x:c r="AB13" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC13" s="16" t="str"/>
-      <x:c r="AD13" s="16" t="str"/>
-      <x:c r="AE13" s="16" t="str"/>
-      <x:c r="AF13" s="16" t="str"/>
-      <x:c r="AG13" s="16" t="str"/>
-      <x:c r="AH13" s="16" t="str"/>
-      <x:c r="AI13" s="16" t="str"/>
-      <x:c r="AJ13" s="14" t="str"/>
-      <x:c r="AK13" s="14" t="str"/>
+      <x:c r="AC13" s="16"/>
+      <x:c r="AD13" s="16"/>
+      <x:c r="AE13" s="16"/>
+      <x:c r="AF13" s="16"/>
+      <x:c r="AG13" s="16"/>
+      <x:c r="AH13" s="16"/>
+      <x:c r="AI13" s="16"/>
+      <x:c r="AJ13" s="14"/>
+      <x:c r="AK13" s="14"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="16" t="n">
@@ -1612,7 +1614,7 @@
         <x:v>wordpress セキュリティ</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>wordpress セキュリティ / wordpressサイト セキュリティ / wordpress の セキュリティ</x:v>
+        <x:v>不正ログイン、脆弱性、改ざん、バックアップ、WAF、復旧手順</x:v>
       </x:c>
       <x:c r="G14" s="16" t="n">
         <x:v>390</x:v>
@@ -1630,28 +1632,28 @@
         <x:v>単独／ピラー</x:v>
       </x:c>
       <x:c r="L14" s="16" t="str">
-        <x:v>WordPressセキュリティ完全ガイド｜狙われる理由から実践対策・被害時対応まで</x:v>
+        <x:v>WordPressセキュリティ完全ガイド｜対策と復旧</x:v>
       </x:c>
       <x:c r="M14" s="16" t="str">
         <x:v>wordpress-security-guide</x:v>
       </x:c>
       <x:c r="N14" s="16" t="str">
-        <x:v>WordPressセキュリティ完全ガイドをテーマに、狙われる理由から実践対策・被害時対応までための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティの全体像を、狙われる入口、予防策、監視、被害時対応の4段階で整理します。自サイトに足りない対策を把握し、詳細記事を読む順番まで決められます。初心者向けの確認順も示します。</x:v>
       </x:c>
       <x:c r="O14" s="16" t="str">
-        <x:v>12,000字</x:v>
+        <x:v>9,000字</x:v>
       </x:c>
       <x:c r="P14" s="16" t="n">
-        <x:v>11640</x:v>
+        <x:v>7650</x:v>
       </x:c>
       <x:c r="Q14" s="16" t="n">
-        <x:v>12360</x:v>
+        <x:v>11700</x:v>
       </x:c>
       <x:c r="R14" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S14" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、インシデント対応</x:v>
       </x:c>
       <x:c r="T14" s="14" t="str">
         <x:v>02,03,06,11,24,32</x:v>
@@ -1666,7 +1668,7 @@
         <x:v>001.png</x:v>
       </x:c>
       <x:c r="X14" s="14" t="str">
-        <x:v>WordPressセキュリティ完全ガイド｜狙われる理由から実践対策・被害時対応まで</x:v>
+        <x:v>WordPressセキュリティ完全ガイド｜対策と復旧</x:v>
       </x:c>
       <x:c r="Y14" s="16" t="str">
         <x:v>執筆済み（要移行）</x:v>
@@ -1680,15 +1682,15 @@
       <x:c r="AB14" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC14" s="16" t="str"/>
-      <x:c r="AD14" s="16" t="str"/>
-      <x:c r="AE14" s="16" t="str"/>
-      <x:c r="AF14" s="16" t="str"/>
-      <x:c r="AG14" s="16" t="str"/>
-      <x:c r="AH14" s="16" t="str"/>
-      <x:c r="AI14" s="16" t="str"/>
-      <x:c r="AJ14" s="14" t="str"/>
-      <x:c r="AK14" s="14" t="str"/>
+      <x:c r="AC14" s="16"/>
+      <x:c r="AD14" s="16"/>
+      <x:c r="AE14" s="16"/>
+      <x:c r="AF14" s="16"/>
+      <x:c r="AG14" s="16"/>
+      <x:c r="AH14" s="16"/>
+      <x:c r="AI14" s="16"/>
+      <x:c r="AJ14" s="14"/>
+      <x:c r="AK14" s="14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="16" t="n">
@@ -1707,7 +1709,7 @@
         <x:v>wordpress セキュリティ プラグイン</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>wordpress セキュリティ プラグイン / wordpress セキュリティ 対策 プラグ イン</x:v>
+        <x:v>Wordfence、SiteGuard、AIOS、Sucuri、WAF、マルウェアスキャン</x:v>
       </x:c>
       <x:c r="G15" s="16" t="n">
         <x:v>320</x:v>
@@ -1725,28 +1727,28 @@
         <x:v>単独／クラスタB ハブ</x:v>
       </x:c>
       <x:c r="L15" s="16" t="str">
-        <x:v>WordPressセキュリティプラグインおすすめ10選｜機能比較と選び方</x:v>
+        <x:v>WordPressセキュリティプラグイン10選｜機能比較</x:v>
       </x:c>
       <x:c r="M15" s="16" t="str">
         <x:v>wordpress-security-plugins</x:v>
       </x:c>
       <x:c r="N15" s="16" t="str">
-        <x:v>WordPressセキュリティプラグインおすすめ10選をテーマに、機能比較と選び方ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ プラグイン10製品を、WAF、ログイン保護、スキャン、通知、バックアップ連携で比較します。サイト規模と必要機能を照らし、過不足のない1製品を選べます。機能の重複も避けやすくなります。</x:v>
       </x:c>
       <x:c r="O15" s="16" t="str">
-        <x:v>12,000字</x:v>
+        <x:v>8,500字</x:v>
       </x:c>
       <x:c r="P15" s="16" t="n">
-        <x:v>11640</x:v>
+        <x:v>7225</x:v>
       </x:c>
       <x:c r="Q15" s="16" t="n">
-        <x:v>12360</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="R15" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S15" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、WAF・サーバー、ログイン防御</x:v>
       </x:c>
       <x:c r="T15" s="14" t="str">
         <x:v>01,06,23,12,15</x:v>
@@ -1761,7 +1763,7 @@
         <x:v>011.png</x:v>
       </x:c>
       <x:c r="X15" s="14" t="str">
-        <x:v>WordPressセキュリティプラグインおすすめ10選｜機能比較と選び方</x:v>
+        <x:v>WordPressセキュリティプラグイン10選｜機能比較</x:v>
       </x:c>
       <x:c r="Y15" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1775,15 +1777,15 @@
       <x:c r="AB15" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC15" s="16" t="str"/>
-      <x:c r="AD15" s="16" t="str"/>
-      <x:c r="AE15" s="16" t="str"/>
-      <x:c r="AF15" s="16" t="str"/>
-      <x:c r="AG15" s="16" t="str"/>
-      <x:c r="AH15" s="16" t="str"/>
-      <x:c r="AI15" s="16" t="str"/>
-      <x:c r="AJ15" s="14" t="str"/>
-      <x:c r="AK15" s="14" t="str"/>
+      <x:c r="AC15" s="16"/>
+      <x:c r="AD15" s="16"/>
+      <x:c r="AE15" s="16"/>
+      <x:c r="AF15" s="16"/>
+      <x:c r="AG15" s="16"/>
+      <x:c r="AH15" s="16"/>
+      <x:c r="AI15" s="16"/>
+      <x:c r="AJ15" s="14"/>
+      <x:c r="AK15" s="14"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="16" t="n">
@@ -1802,7 +1804,7 @@
         <x:v>wordpress セキュリティ対策</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>wordpress セキュリティ対策 / wordpress セキュリティ 対応 / wordpress の セキュリティ 対策</x:v>
+        <x:v>アップデート、強力なパスワード、二要素認証、バックアップ、WAF、権限管理</x:v>
       </x:c>
       <x:c r="G16" s="16" t="n">
         <x:v>210</x:v>
@@ -1820,28 +1822,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L16" s="16" t="str">
-        <x:v>WordPressのセキュリティ対策12選｜優先度順に今日から実施する手順</x:v>
+        <x:v>WordPressセキュリティ対策12選｜優先順位付き</x:v>
       </x:c>
       <x:c r="M16" s="16" t="str">
         <x:v>wordpress-security-measures</x:v>
       </x:c>
       <x:c r="N16" s="16" t="str">
-        <x:v>WordPressのセキュリティ対策12選をテーマに、優先度順に今日から実施する手順ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ対策12項目を、今すぐ行う対策、環境を確認して行う対策、継続運用に分けます。費用と作業時間も踏まえ、自サイトで着手する順番を決められます。最低限の実施ラインも明確になります。</x:v>
       </x:c>
       <x:c r="O16" s="16" t="str">
-        <x:v>10,000字</x:v>
+        <x:v>7,500字</x:v>
       </x:c>
       <x:c r="P16" s="16" t="n">
-        <x:v>9700</x:v>
+        <x:v>6375</x:v>
       </x:c>
       <x:c r="Q16" s="16" t="n">
-        <x:v>10300</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="R16" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S16" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、アップデート運用</x:v>
       </x:c>
       <x:c r="T16" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -1856,7 +1858,7 @@
         <x:v>002.png</x:v>
       </x:c>
       <x:c r="X16" s="14" t="str">
-        <x:v>WordPressのセキュリティ対策12選｜優先度順に今日から実施する手順</x:v>
+        <x:v>WordPressセキュリティ対策12選｜優先順位付き</x:v>
       </x:c>
       <x:c r="Y16" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1870,15 +1872,15 @@
       <x:c r="AB16" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC16" s="16" t="str"/>
-      <x:c r="AD16" s="16" t="str"/>
-      <x:c r="AE16" s="16" t="str"/>
-      <x:c r="AF16" s="16" t="str"/>
-      <x:c r="AG16" s="16" t="str"/>
-      <x:c r="AH16" s="16" t="str"/>
-      <x:c r="AI16" s="16" t="str"/>
-      <x:c r="AJ16" s="14" t="str"/>
-      <x:c r="AK16" s="14" t="str"/>
+      <x:c r="AC16" s="16"/>
+      <x:c r="AD16" s="16"/>
+      <x:c r="AE16" s="16"/>
+      <x:c r="AF16" s="16"/>
+      <x:c r="AG16" s="16"/>
+      <x:c r="AH16" s="16"/>
+      <x:c r="AI16" s="16"/>
+      <x:c r="AJ16" s="14"/>
+      <x:c r="AK16" s="14"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="16" t="n">
@@ -1897,7 +1899,7 @@
         <x:v>wordpress セキュリティ プラグイン おすすめ</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>wordpress セキュリティ プラグイン おすすめ</x:v>
+        <x:v>機能比較、サイト規模、サーバー負荷、競合、サポート、更新頻度</x:v>
       </x:c>
       <x:c r="G17" s="16" t="n">
         <x:v>40</x:v>
@@ -1915,28 +1917,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L17" s="16" t="str">
-        <x:v>目的別WordPressセキュリティプラグインの選び方｜入れるべきは何個か</x:v>
+        <x:v>WordPressセキュリティプラグインおすすめの選び方</x:v>
       </x:c>
       <x:c r="M17" s="16" t="str">
         <x:v>choose-wordpress-security-plugin</x:v>
       </x:c>
       <x:c r="N17" s="16" t="str">
-        <x:v>目的別WordPressセキュリティプラグインの選び方をテーマに、入れるべきは何個かための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ プラグイン おすすめ製品を探す前に、守りたい対象、サーバー負荷、既存WAF、運用人数を確認します。ランキングに頼らず、自サイトに必要な機能を選定できます。導入後の運用負担も見通せます。</x:v>
       </x:c>
       <x:c r="O17" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P17" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q17" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R17" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S17" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、WAF・サーバー、基本対策</x:v>
       </x:c>
       <x:c r="T17" s="14" t="str">
         <x:v>01,06,23,12,15</x:v>
@@ -1951,7 +1953,7 @@
         <x:v>013.png</x:v>
       </x:c>
       <x:c r="X17" s="14" t="str">
-        <x:v>目的別WordPressセキュリティプラグインの選び方｜入れるべきは何個か</x:v>
+        <x:v>WordPressセキュリティプラグインおすすめの選び方</x:v>
       </x:c>
       <x:c r="Y17" s="16" t="str">
         <x:v>未着手</x:v>
@@ -1965,15 +1967,15 @@
       <x:c r="AB17" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC17" s="16" t="str"/>
-      <x:c r="AD17" s="16" t="str"/>
-      <x:c r="AE17" s="16" t="str"/>
-      <x:c r="AF17" s="16" t="str"/>
-      <x:c r="AG17" s="16" t="str"/>
-      <x:c r="AH17" s="16" t="str"/>
-      <x:c r="AI17" s="16" t="str"/>
-      <x:c r="AJ17" s="14" t="str"/>
-      <x:c r="AK17" s="14" t="str"/>
+      <x:c r="AC17" s="16"/>
+      <x:c r="AD17" s="16"/>
+      <x:c r="AE17" s="16"/>
+      <x:c r="AF17" s="16"/>
+      <x:c r="AG17" s="16"/>
+      <x:c r="AH17" s="16"/>
+      <x:c r="AI17" s="16"/>
+      <x:c r="AJ17" s="14"/>
+      <x:c r="AK17" s="14"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="16" t="n">
@@ -1992,7 +1994,7 @@
         <x:v>wordpress セキュリティ 強化</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>wordpress セキュリティ 強化</x:v>
+        <x:v>多層防御、最小権限、WAF、監視ログ、バックアップ、サーバー設定</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
         <x:v>20</x:v>
@@ -2010,28 +2012,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L18" s="16" t="str">
-        <x:v>WordPressのセキュリティを強化する方法｜プラグインに頼らない多層防御</x:v>
+        <x:v>WordPressセキュリティ強化｜多層防御の作り方</x:v>
       </x:c>
       <x:c r="M18" s="16" t="str">
         <x:v>wordpress-security-hardening</x:v>
       </x:c>
       <x:c r="N18" s="16" t="str">
-        <x:v>WordPressのセキュリティを強化する方法をテーマに、プラグインに頼らない多層防御ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 強化を、アカウント、WordPress、サーバー、バックアップの4層で考えます。一つのプラグインに依存せず、侵入・検知・復旧を組み合わせた構成を作れます。不足する層だけを補強できます。</x:v>
       </x:c>
       <x:c r="O18" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P18" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q18" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R18" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S18" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>基本対策、WAF・サーバー、バックアップ</x:v>
       </x:c>
       <x:c r="T18" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2046,7 +2048,7 @@
         <x:v>004.png</x:v>
       </x:c>
       <x:c r="X18" s="14" t="str">
-        <x:v>WordPressのセキュリティを強化する方法｜プラグインに頼らない多層防御</x:v>
+        <x:v>WordPressセキュリティ強化｜多層防御の作り方</x:v>
       </x:c>
       <x:c r="Y18" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2060,15 +2062,15 @@
       <x:c r="AB18" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC18" s="16" t="str"/>
-      <x:c r="AD18" s="16" t="str"/>
-      <x:c r="AE18" s="16" t="str"/>
-      <x:c r="AF18" s="16" t="str"/>
-      <x:c r="AG18" s="16" t="str"/>
-      <x:c r="AH18" s="16" t="str"/>
-      <x:c r="AI18" s="16" t="str"/>
-      <x:c r="AJ18" s="14" t="str"/>
-      <x:c r="AK18" s="14" t="str"/>
+      <x:c r="AC18" s="16"/>
+      <x:c r="AD18" s="16"/>
+      <x:c r="AE18" s="16"/>
+      <x:c r="AF18" s="16"/>
+      <x:c r="AG18" s="16"/>
+      <x:c r="AH18" s="16"/>
+      <x:c r="AI18" s="16"/>
+      <x:c r="AJ18" s="14"/>
+      <x:c r="AK18" s="14"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="16" t="n">
@@ -2087,7 +2089,7 @@
         <x:v>wordpress ログイン セキュリティ</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>wordpress ログイン セキュリティ</x:v>
+        <x:v>ログイン試行制限、二要素認証、CAPTCHA、強力なパスワード、管理者名、通知</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
         <x:v>20</x:v>
@@ -2105,28 +2107,28 @@
         <x:v>単独／クラスタD ハブ</x:v>
       </x:c>
       <x:c r="L19" s="16" t="str">
-        <x:v>WordPressのログインセキュリティ｜攻撃の9割を止める7つの設定</x:v>
+        <x:v>WordPressログインセキュリティ｜7つの基本設定</x:v>
       </x:c>
       <x:c r="M19" s="16" t="str">
         <x:v>wordpress-login-security</x:v>
       </x:c>
       <x:c r="N19" s="16" t="str">
-        <x:v>WordPressのログインセキュリティをテーマに、攻撃の9割を止める7つの設定ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress ログイン セキュリティを高める7設定として、試行回数制限、二要素認証、CAPTCHA、管理者名、通知を確認します。自サイトに必要な防御と運用負荷のバランスを決められます。設定後の確認方法も押さえられます。</x:v>
       </x:c>
       <x:c r="O19" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P19" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q19" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R19" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; ログインと管理画面</x:v>
       </x:c>
       <x:c r="S19" s="14" t="str">
-        <x:v>WordPress、セキュリティ、ログイン対策</x:v>
+        <x:v>ログイン防御、基本対策、セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="T19" s="14" t="str">
         <x:v>01,06,23,16,38</x:v>
@@ -2141,7 +2143,7 @@
         <x:v>035.png</x:v>
       </x:c>
       <x:c r="X19" s="14" t="str">
-        <x:v>WordPressのログインセキュリティ｜攻撃の9割を止める7つの設定</x:v>
+        <x:v>WordPressログインセキュリティ｜7つの基本設定</x:v>
       </x:c>
       <x:c r="Y19" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2155,15 +2157,15 @@
       <x:c r="AB19" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC19" s="16" t="str"/>
-      <x:c r="AD19" s="16" t="str"/>
-      <x:c r="AE19" s="16" t="str"/>
-      <x:c r="AF19" s="16" t="str"/>
-      <x:c r="AG19" s="16" t="str"/>
-      <x:c r="AH19" s="16" t="str"/>
-      <x:c r="AI19" s="16" t="str"/>
-      <x:c r="AJ19" s="14" t="str"/>
-      <x:c r="AK19" s="14" t="str"/>
+      <x:c r="AC19" s="16"/>
+      <x:c r="AD19" s="16"/>
+      <x:c r="AE19" s="16"/>
+      <x:c r="AF19" s="16"/>
+      <x:c r="AG19" s="16"/>
+      <x:c r="AH19" s="16"/>
+      <x:c r="AI19" s="16"/>
+      <x:c r="AJ19" s="14"/>
+      <x:c r="AK19" s="14"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="n">
@@ -2182,7 +2184,7 @@
         <x:v>wordpress ログイン セキュリティ プラグイン</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>wordpress ログイン セキュリティ プラグイン</x:v>
+        <x:v>二要素認証、ログイン試行制限、CAPTCHA、ログイン通知、ロックアウト、復旧</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
         <x:v>20</x:v>
@@ -2200,28 +2202,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L20" s="16" t="str">
-        <x:v>ログイン保護に使えるWordPressプラグイン比較｜二要素認証・回数制限</x:v>
+        <x:v>WordPressログインセキュリティプラグイン比較</x:v>
       </x:c>
       <x:c r="M20" s="16" t="str">
         <x:v>wordpress-login-security-plugins</x:v>
       </x:c>
       <x:c r="N20" s="16" t="str">
-        <x:v>ログイン保護に使えるWordPressプラグイン比較をテーマに、二要素認証・回数制限ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress ログイン セキュリティ プラグインを、二要素認証、回数制限、CAPTCHA、通知、復旧方法で比較します。多機能製品ではなく、ログイン保護に必要な機能だけを選べます。ロックアウト時の備えも比較できます。</x:v>
       </x:c>
       <x:c r="O20" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P20" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q20" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R20" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S20" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>ログイン防御、セキュリティプラグイン、基本対策</x:v>
       </x:c>
       <x:c r="T20" s="14" t="str">
         <x:v>01,06,23,12,15</x:v>
@@ -2236,7 +2238,7 @@
         <x:v>016.png</x:v>
       </x:c>
       <x:c r="X20" s="14" t="str">
-        <x:v>ログイン保護に使えるWordPressプラグイン比較｜二要素認証・回数制限</x:v>
+        <x:v>WordPressログインセキュリティプラグイン比較</x:v>
       </x:c>
       <x:c r="Y20" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2250,15 +2252,15 @@
       <x:c r="AB20" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC20" s="16" t="str"/>
-      <x:c r="AD20" s="16" t="str"/>
-      <x:c r="AE20" s="16" t="str"/>
-      <x:c r="AF20" s="16" t="str"/>
-      <x:c r="AG20" s="16" t="str"/>
-      <x:c r="AH20" s="16" t="str"/>
-      <x:c r="AI20" s="16" t="str"/>
-      <x:c r="AJ20" s="14" t="str"/>
-      <x:c r="AK20" s="14" t="str"/>
+      <x:c r="AC20" s="16"/>
+      <x:c r="AD20" s="16"/>
+      <x:c r="AE20" s="16"/>
+      <x:c r="AF20" s="16"/>
+      <x:c r="AG20" s="16"/>
+      <x:c r="AH20" s="16"/>
+      <x:c r="AI20" s="16"/>
+      <x:c r="AJ20" s="14"/>
+      <x:c r="AK20" s="14"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="n">
@@ -2277,7 +2279,7 @@
         <x:v>wordpress セキュリティ おすすめ</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>wordpress セキュリティ おすすめ</x:v>
+        <x:v>個人ブログ、企業サイト、ECサイト、運用人数、予算、外部監視</x:v>
       </x:c>
       <x:c r="G21" s="16" t="n">
         <x:v>10</x:v>
@@ -2295,28 +2297,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L21" s="16" t="str">
-        <x:v>WordPressセキュリティのおすすめ対策・ツールまとめ｜規模別の最適解</x:v>
+        <x:v>WordPressセキュリティのおすすめ対策｜規模別</x:v>
       </x:c>
       <x:c r="M21" s="16" t="str">
         <x:v>wordpress-security-tools-by-size</x:v>
       </x:c>
       <x:c r="N21" s="16" t="str">
-        <x:v>WordPressセキュリティのおすすめ対策・ツールまとめをテーマに、規模別の最適解ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ おすすめ構成を、個人ブログ、企業サイト、EC・会員サイトの3段階で提示します。扱う情報、更新頻度、予算から、必要な対策と過剰な対策を見分けられます。運用規模に合う構成表として使えます。</x:v>
       </x:c>
       <x:c r="O21" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P21" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q21" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R21" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S21" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、個人情報保護</x:v>
       </x:c>
       <x:c r="T21" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2331,7 +2333,7 @@
         <x:v>010.png</x:v>
       </x:c>
       <x:c r="X21" s="14" t="str">
-        <x:v>WordPressセキュリティのおすすめ対策・ツールまとめ｜規模別の最適解</x:v>
+        <x:v>WordPressセキュリティのおすすめ対策｜規模別</x:v>
       </x:c>
       <x:c r="Y21" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2345,15 +2347,15 @@
       <x:c r="AB21" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC21" s="16" t="str"/>
-      <x:c r="AD21" s="16" t="str"/>
-      <x:c r="AE21" s="16" t="str"/>
-      <x:c r="AF21" s="16" t="str"/>
-      <x:c r="AG21" s="16" t="str"/>
-      <x:c r="AH21" s="16" t="str"/>
-      <x:c r="AI21" s="16" t="str"/>
-      <x:c r="AJ21" s="14" t="str"/>
-      <x:c r="AK21" s="14" t="str"/>
+      <x:c r="AC21" s="16"/>
+      <x:c r="AD21" s="16"/>
+      <x:c r="AE21" s="16"/>
+      <x:c r="AF21" s="16"/>
+      <x:c r="AG21" s="16"/>
+      <x:c r="AH21" s="16"/>
+      <x:c r="AI21" s="16"/>
+      <x:c r="AJ21" s="14"/>
+      <x:c r="AK21" s="14"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="n">
@@ -2372,7 +2374,7 @@
         <x:v>wordpress セキュリティ 保護 なし</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>wordpress セキュリティ 保護 なし</x:v>
+        <x:v>SSL化、HTTPS、混在コンテンツ、証明書、サイトURL、リダイレクト</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
         <x:v>10</x:v>
@@ -2390,28 +2392,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L22" s="16" t="str">
-        <x:v>WordPressで「保護されていない通信」と出る原因と直し方</x:v>
+        <x:v>WordPressセキュリティ｜保護されていない通信の直し方</x:v>
       </x:c>
       <x:c r="M22" s="16" t="str">
         <x:v>wordpress-not-secure-connection</x:v>
       </x:c>
       <x:c r="N22" s="16" t="str">
-        <x:v>WordPressで「保護されていない通信」と出る原因と直し方について、必要な設定、判断基準、注意点を実務目線で解説します。WordPress運用者が迷いやすい点を整理し、次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 保護 なしと表示される原因を、SSL証明書、URL設定、混在コンテンツ、リダイレクトに分けます。ブラウザ警告の原因箇所を特定し、HTTPSへ統一できます。修正後の確認ポイントも押さえられます。</x:v>
       </x:c>
       <x:c r="O22" s="16" t="str">
-        <x:v>6,000字</x:v>
+        <x:v>4,500字</x:v>
       </x:c>
       <x:c r="P22" s="16" t="n">
-        <x:v>5820</x:v>
+        <x:v>3825</x:v>
       </x:c>
       <x:c r="Q22" s="16" t="n">
-        <x:v>6180</x:v>
+        <x:v>5850</x:v>
       </x:c>
       <x:c r="R22" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S22" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、WAF・サーバー、設定監査</x:v>
       </x:c>
       <x:c r="T22" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2426,7 +2428,7 @@
         <x:v>007.png</x:v>
       </x:c>
       <x:c r="X22" s="14" t="str">
-        <x:v>WordPressで「保護されていない通信」と出る原因と直し方</x:v>
+        <x:v>WordPressセキュリティ｜保護されていない通信の直し方</x:v>
       </x:c>
       <x:c r="Y22" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2440,15 +2442,15 @@
       <x:c r="AB22" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC22" s="16" t="str"/>
-      <x:c r="AD22" s="16" t="str"/>
-      <x:c r="AE22" s="16" t="str"/>
-      <x:c r="AF22" s="16" t="str"/>
-      <x:c r="AG22" s="16" t="str"/>
-      <x:c r="AH22" s="16" t="str"/>
-      <x:c r="AI22" s="16" t="str"/>
-      <x:c r="AJ22" s="14" t="str"/>
-      <x:c r="AK22" s="14" t="str"/>
+      <x:c r="AC22" s="16"/>
+      <x:c r="AD22" s="16"/>
+      <x:c r="AE22" s="16"/>
+      <x:c r="AF22" s="16"/>
+      <x:c r="AG22" s="16"/>
+      <x:c r="AH22" s="16"/>
+      <x:c r="AI22" s="16"/>
+      <x:c r="AJ22" s="14"/>
+      <x:c r="AK22" s="14"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="n">
@@ -2467,7 +2469,7 @@
         <x:v>wordpress セキュリティリスク</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>wordpress セキュリティリスク</x:v>
+        <x:v>サイト改ざん、情報漏えい、マルウェア、SEOスパム、アカウント乗っ取り、信用低下</x:v>
       </x:c>
       <x:c r="G23" s="16" t="n">
         <x:v>20</x:v>
@@ -2485,28 +2487,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L23" s="16" t="str">
-        <x:v>WordPressのセキュリティリスクを放置するとどうなるか｜想定被害の全体像</x:v>
+        <x:v>WordPressセキュリティリスク｜放置時の被害</x:v>
       </x:c>
       <x:c r="M23" s="16" t="str">
         <x:v>wordpress-security-risks</x:v>
       </x:c>
       <x:c r="N23" s="16" t="str">
-        <x:v>WordPressのセキュリティリスクを放置するとどうなるかをテーマに、想定被害の全体像ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティリスクを、改ざん、情報漏えい、SEOスパム、踏み台化、復旧費用の観点で整理します。発生可能性と影響度を照らし、対策を後回しにできるか判断できます。経営判断に必要な影響も見通せます。</x:v>
       </x:c>
       <x:c r="O23" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P23" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q23" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R23" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S23" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、インシデント対応、脆弱性管理</x:v>
       </x:c>
       <x:c r="T23" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2521,7 +2523,7 @@
         <x:v>034.png</x:v>
       </x:c>
       <x:c r="X23" s="14" t="str">
-        <x:v>WordPressのセキュリティリスクを放置するとどうなるか｜想定被害の全体像</x:v>
+        <x:v>WordPressセキュリティリスク｜放置時の被害</x:v>
       </x:c>
       <x:c r="Y23" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2535,15 +2537,15 @@
       <x:c r="AB23" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC23" s="16" t="str"/>
-      <x:c r="AD23" s="16" t="str"/>
-      <x:c r="AE23" s="16" t="str"/>
-      <x:c r="AF23" s="16" t="str"/>
-      <x:c r="AG23" s="16" t="str"/>
-      <x:c r="AH23" s="16" t="str"/>
-      <x:c r="AI23" s="16" t="str"/>
-      <x:c r="AJ23" s="14" t="str"/>
-      <x:c r="AK23" s="14" t="str"/>
+      <x:c r="AC23" s="16"/>
+      <x:c r="AD23" s="16"/>
+      <x:c r="AE23" s="16"/>
+      <x:c r="AF23" s="16"/>
+      <x:c r="AG23" s="16"/>
+      <x:c r="AH23" s="16"/>
+      <x:c r="AI23" s="16"/>
+      <x:c r="AJ23" s="14"/>
+      <x:c r="AK23" s="14"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="16" t="n">
@@ -2562,7 +2564,7 @@
         <x:v>wordpress セキュリティ 弱い</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>wordpress セキュリティ 弱い</x:v>
+        <x:v>シェア率、プラグイン、更新不足、総当たり攻撃、脆弱性、運用ミス</x:v>
       </x:c>
       <x:c r="G24" s="16" t="n">
         <x:v>10</x:v>
@@ -2580,28 +2582,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L24" s="16" t="str">
-        <x:v>WordPressはセキュリティが弱いのか｜狙われる本当の理由をデータで検証</x:v>
+        <x:v>WordPressセキュリティは弱い？狙われる理由</x:v>
       </x:c>
       <x:c r="M24" s="16" t="str">
         <x:v>is-wordpress-security-weak</x:v>
       </x:c>
       <x:c r="N24" s="16" t="str">
-        <x:v>WordPressはセキュリティが弱いのかをテーマに、狙われる本当の理由をデータで検証ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 弱いと言われる理由を、普及規模、拡張機能、更新不足、運用設定に分けます。本体の問題と管理上の問題を切り分け、利用を続けるリスクを判断できます。必要な補強策まで整理できます。</x:v>
       </x:c>
       <x:c r="O24" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P24" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q24" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R24" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S24" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、脆弱性管理、アップデート運用</x:v>
       </x:c>
       <x:c r="T24" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2616,7 +2618,7 @@
         <x:v>009.png</x:v>
       </x:c>
       <x:c r="X24" s="14" t="str">
-        <x:v>WordPressはセキュリティが弱いのか｜狙われる本当の理由をデータで検証</x:v>
+        <x:v>WordPressセキュリティは弱い？狙われる理由</x:v>
       </x:c>
       <x:c r="Y24" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2630,15 +2632,15 @@
       <x:c r="AB24" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC24" s="16" t="str"/>
-      <x:c r="AD24" s="16" t="str"/>
-      <x:c r="AE24" s="16" t="str"/>
-      <x:c r="AF24" s="16" t="str"/>
-      <x:c r="AG24" s="16" t="str"/>
-      <x:c r="AH24" s="16" t="str"/>
-      <x:c r="AI24" s="16" t="str"/>
-      <x:c r="AJ24" s="14" t="str"/>
-      <x:c r="AK24" s="14" t="str"/>
+      <x:c r="AC24" s="16"/>
+      <x:c r="AD24" s="16"/>
+      <x:c r="AE24" s="16"/>
+      <x:c r="AF24" s="16"/>
+      <x:c r="AG24" s="16"/>
+      <x:c r="AH24" s="16"/>
+      <x:c r="AI24" s="16"/>
+      <x:c r="AJ24" s="14"/>
+      <x:c r="AK24" s="14"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="n">
@@ -2657,7 +2659,7 @@
         <x:v>wordpress セキュリティ ホール</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>wordpress セキュリティ ホール</x:v>
+        <x:v>コア、テーマ、プラグイン、設定不備、サーバー、サプライチェーン</x:v>
       </x:c>
       <x:c r="G25" s="16" t="n">
         <x:v>10</x:v>
@@ -2675,28 +2677,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L25" s="16" t="str">
-        <x:v>WordPressのセキュリティホールはどこにできるか｜構造から理解する</x:v>
+        <x:v>WordPressセキュリティホールの発生箇所</x:v>
       </x:c>
       <x:c r="M25" s="16" t="str">
         <x:v>wordpress-security-holes</x:v>
       </x:c>
       <x:c r="N25" s="16" t="str">
-        <x:v>WordPressのセキュリティホールはどこにできるかをテーマに、構造から理解するための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ ホールが生じる場所を、コア、テーマ、プラグイン、設定、サーバーの5層で示します。脆弱性と設定ミスを混同せず、確認先と担当範囲を特定できます。点検の担当者も割り当てやすくなります。</x:v>
       </x:c>
       <x:c r="O25" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P25" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q25" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R25" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S25" s="14" t="str">
-        <x:v>WordPress、セキュリティ、脆弱性対策</x:v>
+        <x:v>脆弱性管理、設定監査、WAF・サーバー</x:v>
       </x:c>
       <x:c r="T25" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2711,7 +2713,7 @@
         <x:v>025.png</x:v>
       </x:c>
       <x:c r="X25" s="14" t="str">
-        <x:v>WordPressのセキュリティホールはどこにできるか｜構造から理解する</x:v>
+        <x:v>WordPressセキュリティホールの発生箇所</x:v>
       </x:c>
       <x:c r="Y25" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2725,15 +2727,15 @@
       <x:c r="AB25" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC25" s="16" t="str"/>
-      <x:c r="AD25" s="16" t="str"/>
-      <x:c r="AE25" s="16" t="str"/>
-      <x:c r="AF25" s="16" t="str"/>
-      <x:c r="AG25" s="16" t="str"/>
-      <x:c r="AH25" s="16" t="str"/>
-      <x:c r="AI25" s="16" t="str"/>
-      <x:c r="AJ25" s="14" t="str"/>
-      <x:c r="AK25" s="14" t="str"/>
+      <x:c r="AC25" s="16"/>
+      <x:c r="AD25" s="16"/>
+      <x:c r="AE25" s="16"/>
+      <x:c r="AF25" s="16"/>
+      <x:c r="AG25" s="16"/>
+      <x:c r="AH25" s="16"/>
+      <x:c r="AI25" s="16"/>
+      <x:c r="AJ25" s="14"/>
+      <x:c r="AK25" s="14"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="n">
@@ -2752,7 +2754,7 @@
         <x:v>wordpress サーバー セキュリティ</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>wordpress サーバー セキュリティ</x:v>
+        <x:v>PHPバージョン、ファイル権限、WAF、SSH、ログ監視、レンタルサーバー</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
         <x:v>10</x:v>
@@ -2770,28 +2772,28 @@
         <x:v>単独／クラスタE ハブ</x:v>
       </x:c>
       <x:c r="L26" s="16" t="str">
-        <x:v>WordPressのサーバー側セキュリティ｜責任分界点と設定すべき項目</x:v>
+        <x:v>WordPressサーバーセキュリティ｜責任分界点</x:v>
       </x:c>
       <x:c r="M26" s="16" t="str">
         <x:v>wordpress-server-security</x:v>
       </x:c>
       <x:c r="N26" s="16" t="str">
-        <x:v>WordPressのサーバー側セキュリティをテーマに、責任分界点と設定すべき項目ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress サーバー セキュリティで確認するPHP、ファイル権限、WAF、SSH、ログを整理します。レンタルサーバー事業者と利用者の責任を分け、自分で設定すべき範囲を判断できます。保守契約で確認する点も分かります。</x:v>
       </x:c>
       <x:c r="O26" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P26" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q26" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R26" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S26" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サーバーセキュリティ</x:v>
+        <x:v>WAF・サーバー、設定監査、アップデート運用</x:v>
       </x:c>
       <x:c r="T26" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2806,7 +2808,7 @@
         <x:v>040.png</x:v>
       </x:c>
       <x:c r="X26" s="14" t="str">
-        <x:v>WordPressのサーバー側セキュリティ｜責任分界点と設定すべき項目</x:v>
+        <x:v>WordPressサーバーセキュリティ｜責任分界点</x:v>
       </x:c>
       <x:c r="Y26" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2820,15 +2822,15 @@
       <x:c r="AB26" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC26" s="16" t="str"/>
-      <x:c r="AD26" s="16" t="str"/>
-      <x:c r="AE26" s="16" t="str"/>
-      <x:c r="AF26" s="16" t="str"/>
-      <x:c r="AG26" s="16" t="str"/>
-      <x:c r="AH26" s="16" t="str"/>
-      <x:c r="AI26" s="16" t="str"/>
-      <x:c r="AJ26" s="14" t="str"/>
-      <x:c r="AK26" s="14" t="str"/>
+      <x:c r="AC26" s="16"/>
+      <x:c r="AD26" s="16"/>
+      <x:c r="AE26" s="16"/>
+      <x:c r="AF26" s="16"/>
+      <x:c r="AG26" s="16"/>
+      <x:c r="AH26" s="16"/>
+      <x:c r="AI26" s="16"/>
+      <x:c r="AJ26" s="14"/>
+      <x:c r="AK26" s="14"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="16" t="n">
@@ -2847,7 +2849,7 @@
         <x:v>これからのWordPressセキュリティ本格講座</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>これから の wordpress セキュリティ 本格 講座 / wordpress セキュリティ 本</x:v>
+        <x:v>書籍レビュー、学習順序、初心者向け、実践演習、公式ドキュメント、講座比較</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
         <x:v>10</x:v>
@@ -2865,28 +2867,28 @@
         <x:v>単独／直近急上昇。書籍レビュー</x:v>
       </x:c>
       <x:c r="L27" s="16" t="str">
-        <x:v>WordPressセキュリティの学習リソース｜書籍・講座レビュー</x:v>
+        <x:v>これからのWordPressセキュリティ本格講座をレビュー</x:v>
       </x:c>
       <x:c r="M27" s="16" t="str">
         <x:v>wordpress-security-learning-resources</x:v>
       </x:c>
       <x:c r="N27" s="16" t="str">
-        <x:v>WordPressセキュリティの学習リソースをテーマに、書籍・講座レビューための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>これからのWordPressセキュリティ本格講座の対象読者、扱う分野、実践性を確認します。公式資料やオンライン講座との違いも比べ、自分の知識レベルに合う教材か判断できます。購入前の確認材料として使えます。</x:v>
       </x:c>
       <x:c r="O27" s="16" t="str">
-        <x:v>6,000字</x:v>
+        <x:v>4,500字</x:v>
       </x:c>
       <x:c r="P27" s="16" t="n">
-        <x:v>5820</x:v>
+        <x:v>3825</x:v>
       </x:c>
       <x:c r="Q27" s="16" t="n">
-        <x:v>6180</x:v>
+        <x:v>5850</x:v>
       </x:c>
       <x:c r="R27" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S27" s="14" t="str">
-        <x:v>WordPress、セキュリティ</x:v>
+        <x:v>基本対策、設定監査、アップデート運用</x:v>
       </x:c>
       <x:c r="T27" s="14" t="str">
         <x:v>01,06,23</x:v>
@@ -2901,7 +2903,7 @@
         <x:v>054.png</x:v>
       </x:c>
       <x:c r="X27" s="14" t="str">
-        <x:v>WordPressセキュリティの学習リソース｜書籍・講座レビュー</x:v>
+        <x:v>これからのWordPressセキュリティ本格講座をレビュー</x:v>
       </x:c>
       <x:c r="Y27" s="16" t="str">
         <x:v>未着手</x:v>
@@ -2915,15 +2917,15 @@
       <x:c r="AB27" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC27" s="16" t="str"/>
-      <x:c r="AD27" s="16" t="str"/>
-      <x:c r="AE27" s="16" t="str"/>
-      <x:c r="AF27" s="16" t="str"/>
-      <x:c r="AG27" s="16" t="str"/>
-      <x:c r="AH27" s="16" t="str"/>
-      <x:c r="AI27" s="16" t="str"/>
-      <x:c r="AJ27" s="14" t="str"/>
-      <x:c r="AK27" s="14" t="str"/>
+      <x:c r="AC27" s="16"/>
+      <x:c r="AD27" s="16"/>
+      <x:c r="AE27" s="16"/>
+      <x:c r="AF27" s="16"/>
+      <x:c r="AG27" s="16"/>
+      <x:c r="AH27" s="16"/>
+      <x:c r="AI27" s="16"/>
+      <x:c r="AJ27" s="14"/>
+      <x:c r="AK27" s="14"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="n">
@@ -2942,7 +2944,7 @@
         <x:v>wordpress セキュリティ 事故</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>wordpress セキュリティ 事故</x:v>
+        <x:v>サイト改ざん、個人情報漏えい、不正アクセス、原因分析、再発防止、初動対応</x:v>
       </x:c>
       <x:c r="G28" s="16" t="n">
         <x:v>10</x:v>
@@ -2960,28 +2962,28 @@
         <x:v>単独／一次情報で差別化</x:v>
       </x:c>
       <x:c r="L28" s="16" t="str">
-        <x:v>WordPressのセキュリティ事故事例｜改ざん・情報漏えいの実例と教訓</x:v>
+        <x:v>WordPressセキュリティ事故｜実例と教訓</x:v>
       </x:c>
       <x:c r="M28" s="16" t="str">
         <x:v>wordpress-security-incidents</x:v>
       </x:c>
       <x:c r="N28" s="16" t="str">
-        <x:v>WordPressのセキュリティ事故事例をテーマに、改ざん・情報漏えいの実例と教訓ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ 事故を、改ざん、情報漏えい、不正送信、踏み台化の4類型で確認します。公表資料から侵入口と対応の遅れを読み取り、自サイトの再発防止策を選べます。社内報告に必要な観点も把握できます。</x:v>
       </x:c>
       <x:c r="O28" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P28" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q28" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R28" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S28" s="14" t="str">
-        <x:v>WordPress、セキュリティ、インシデント対応</x:v>
+        <x:v>インシデント対応、攻撃対策、個人情報保護</x:v>
       </x:c>
       <x:c r="T28" s="14" t="str">
         <x:v>01,32,33</x:v>
@@ -2996,7 +2998,7 @@
         <x:v>028.png</x:v>
       </x:c>
       <x:c r="X28" s="14" t="str">
-        <x:v>WordPressのセキュリティ事故事例｜改ざん・情報漏えいの実例と教訓</x:v>
+        <x:v>WordPressセキュリティ事故｜実例と教訓</x:v>
       </x:c>
       <x:c r="Y28" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3010,15 +3012,15 @@
       <x:c r="AB28" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC28" s="16" t="str"/>
-      <x:c r="AD28" s="16" t="str"/>
-      <x:c r="AE28" s="16" t="str"/>
-      <x:c r="AF28" s="16" t="str"/>
-      <x:c r="AG28" s="16" t="str"/>
-      <x:c r="AH28" s="16" t="str"/>
-      <x:c r="AI28" s="16" t="str"/>
-      <x:c r="AJ28" s="14" t="str"/>
-      <x:c r="AK28" s="14" t="str"/>
+      <x:c r="AC28" s="16"/>
+      <x:c r="AD28" s="16"/>
+      <x:c r="AE28" s="16"/>
+      <x:c r="AF28" s="16"/>
+      <x:c r="AG28" s="16"/>
+      <x:c r="AH28" s="16"/>
+      <x:c r="AI28" s="16"/>
+      <x:c r="AJ28" s="14"/>
+      <x:c r="AK28" s="14"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="n">
@@ -3033,8 +3035,10 @@
       <x:c r="D29" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E29" s="14" t="str"/>
-      <x:c r="F29" s="14" t="str"/>
+      <x:c r="E29" s="14"/>
+      <x:c r="F29" s="14" t="str">
+        <x:v>総当たり攻撃、ログイン試行、アクセスログ、XML-RPC、レート制限、IP遮断</x:v>
+      </x:c>
       <x:c r="G29" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3051,28 +3055,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L29" s="16" t="str">
-        <x:v>WordPressへのブルートフォース攻撃｜ログで見る実態と遮断方法</x:v>
+        <x:v>WordPressブルートフォース攻撃の見分け方</x:v>
       </x:c>
       <x:c r="M29" s="16" t="str">
         <x:v>wordpress-brute-force-attack</x:v>
       </x:c>
       <x:c r="N29" s="16" t="str">
-        <x:v>WordPressへのブルートフォース攻撃をテーマに、ログで見る実態と遮断方法ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WordPressへのブルートフォース攻撃を、ログイン失敗回数、送信元IP、対象URL、XML-RPCアクセスから見分けます。誤遮断を避けながら、回数制限・CAPTCHA・WAFを選択できます。ログ確認の着眼点も身につきます。</x:v>
       </x:c>
       <x:c r="O29" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P29" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q29" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R29" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S29" s="14" t="str">
-        <x:v>WordPress、セキュリティ、インシデント対応</x:v>
+        <x:v>攻撃対策、ログイン防御、WAF・サーバー</x:v>
       </x:c>
       <x:c r="T29" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -3087,7 +3091,7 @@
         <x:v>030.png</x:v>
       </x:c>
       <x:c r="X29" s="14" t="str">
-        <x:v>WordPressへのブルートフォース攻撃｜ログで見る実態と遮断方法</x:v>
+        <x:v>WordPressブルートフォース攻撃の見分け方</x:v>
       </x:c>
       <x:c r="Y29" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3101,15 +3105,15 @@
       <x:c r="AB29" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC29" s="16" t="str"/>
-      <x:c r="AD29" s="16" t="str"/>
-      <x:c r="AE29" s="16" t="str"/>
-      <x:c r="AF29" s="16" t="str"/>
-      <x:c r="AG29" s="16" t="str"/>
-      <x:c r="AH29" s="16" t="str"/>
-      <x:c r="AI29" s="16" t="str"/>
-      <x:c r="AJ29" s="14" t="str"/>
-      <x:c r="AK29" s="14" t="str"/>
+      <x:c r="AC29" s="16"/>
+      <x:c r="AD29" s="16"/>
+      <x:c r="AE29" s="16"/>
+      <x:c r="AF29" s="16"/>
+      <x:c r="AG29" s="16"/>
+      <x:c r="AH29" s="16"/>
+      <x:c r="AI29" s="16"/>
+      <x:c r="AJ29" s="14"/>
+      <x:c r="AK29" s="14"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="16" t="n">
@@ -3124,8 +3128,10 @@
       <x:c r="D30" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E30" s="14" t="str"/>
-      <x:c r="F30" s="14" t="str"/>
+      <x:c r="E30" s="14"/>
+      <x:c r="F30" s="14" t="str">
+        <x:v>入力値検証、エスケープ、プリペアドステートメント、nonce、WAF、プラグイン脆弱性</x:v>
+      </x:c>
       <x:c r="G30" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3142,28 +3148,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L30" s="16" t="str">
-        <x:v>WordPressを狙うSQLインジェクション・XSS｜発生条件と防御策</x:v>
+        <x:v>WordPressのSQLインジェクション・XSS対策</x:v>
       </x:c>
       <x:c r="M30" s="16" t="str">
         <x:v>wordpress-sql-injection-xss</x:v>
       </x:c>
       <x:c r="N30" s="16" t="str">
-        <x:v>WordPressを狙うSQLインジェクション・XSSをテーマに、発生条件と防御策ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WordPressでSQLインジェクションとXSSが起きる条件を、入力処理、出力処理、プラグイン実装から整理します。開発側の修正と運用側の更新・WAFを分け、適切な防御を選べます。脆弱な実装の見分け方も分かります。</x:v>
       </x:c>
       <x:c r="O30" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P30" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q30" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R30" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S30" s="14" t="str">
-        <x:v>WordPress、セキュリティ、インシデント対応</x:v>
+        <x:v>攻撃対策、API・開発、脆弱性管理</x:v>
       </x:c>
       <x:c r="T30" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -3178,7 +3184,7 @@
         <x:v>031.png</x:v>
       </x:c>
       <x:c r="X30" s="14" t="str">
-        <x:v>WordPressを狙うSQLインジェクション・XSS｜発生条件と防御策</x:v>
+        <x:v>WordPressのSQLインジェクション・XSS対策</x:v>
       </x:c>
       <x:c r="Y30" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3192,15 +3198,15 @@
       <x:c r="AB30" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC30" s="16" t="str"/>
-      <x:c r="AD30" s="16" t="str"/>
-      <x:c r="AE30" s="16" t="str"/>
-      <x:c r="AF30" s="16" t="str"/>
-      <x:c r="AG30" s="16" t="str"/>
-      <x:c r="AH30" s="16" t="str"/>
-      <x:c r="AI30" s="16" t="str"/>
-      <x:c r="AJ30" s="14" t="str"/>
-      <x:c r="AK30" s="14" t="str"/>
+      <x:c r="AC30" s="16"/>
+      <x:c r="AD30" s="16"/>
+      <x:c r="AE30" s="16"/>
+      <x:c r="AF30" s="16"/>
+      <x:c r="AG30" s="16"/>
+      <x:c r="AH30" s="16"/>
+      <x:c r="AI30" s="16"/>
+      <x:c r="AJ30" s="14"/>
+      <x:c r="AK30" s="14"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="16" t="n">
@@ -3215,8 +3221,10 @@
       <x:c r="D31" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E31" s="14" t="str"/>
-      <x:c r="F31" s="14" t="str"/>
+      <x:c r="E31" s="14"/>
+      <x:c r="F31" s="14" t="str">
+        <x:v>緊急停止、証拠保全、バックアップ復元、管理者変更、マルウェア、再発防止</x:v>
+      </x:c>
       <x:c r="G31" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3233,28 +3241,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L31" s="16" t="str">
-        <x:v>WordPressサイトが改ざんされたときの対処手順｜切り分けから復旧まで</x:v>
+        <x:v>WordPress改ざん時の復旧手順｜初動から再開まで</x:v>
       </x:c>
       <x:c r="M31" s="16" t="str">
         <x:v>wordpress-site-defacement-recovery</x:v>
       </x:c>
       <x:c r="N31" s="16" t="str">
-        <x:v>WordPressサイトが改ざんされたときの対処手順をテーマに、切り分けから復旧までための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WordPressサイトの改ざんを発見した直後に、公開停止、証拠保全、侵入口確認、復元、認証情報変更を行う順番を示します。消す前に残す情報を理解し、安全な再公開を判断できます。関係者へ伝える項目も整理できます。</x:v>
       </x:c>
       <x:c r="O31" s="16" t="str">
-        <x:v>10,000字</x:v>
+        <x:v>7,500字</x:v>
       </x:c>
       <x:c r="P31" s="16" t="n">
-        <x:v>9700</x:v>
+        <x:v>6375</x:v>
       </x:c>
       <x:c r="Q31" s="16" t="n">
-        <x:v>10300</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="R31" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S31" s="14" t="str">
-        <x:v>WordPress、セキュリティ、インシデント対応</x:v>
+        <x:v>インシデント対応、マルウェア対策、バックアップ</x:v>
       </x:c>
       <x:c r="T31" s="14" t="str">
         <x:v>01,33</x:v>
@@ -3269,7 +3277,7 @@
         <x:v>032.png</x:v>
       </x:c>
       <x:c r="X31" s="14" t="str">
-        <x:v>WordPressサイトが改ざんされたときの対処手順｜切り分けから復旧まで</x:v>
+        <x:v>WordPress改ざん時の復旧手順｜初動から再開まで</x:v>
       </x:c>
       <x:c r="Y31" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3283,15 +3291,15 @@
       <x:c r="AB31" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC31" s="16" t="str"/>
-      <x:c r="AD31" s="16" t="str"/>
-      <x:c r="AE31" s="16" t="str"/>
-      <x:c r="AF31" s="16" t="str"/>
-      <x:c r="AG31" s="16" t="str"/>
-      <x:c r="AH31" s="16" t="str"/>
-      <x:c r="AI31" s="16" t="str"/>
-      <x:c r="AJ31" s="14" t="str"/>
-      <x:c r="AK31" s="14" t="str"/>
+      <x:c r="AC31" s="16"/>
+      <x:c r="AD31" s="16"/>
+      <x:c r="AE31" s="16"/>
+      <x:c r="AF31" s="16"/>
+      <x:c r="AG31" s="16"/>
+      <x:c r="AH31" s="16"/>
+      <x:c r="AI31" s="16"/>
+      <x:c r="AJ31" s="14"/>
+      <x:c r="AK31" s="14"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="16" t="n">
@@ -3306,8 +3314,10 @@
       <x:c r="D32" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E32" s="14" t="str"/>
-      <x:c r="F32" s="14" t="str"/>
+      <x:c r="E32" s="14"/>
+      <x:c r="F32" s="14" t="str">
+        <x:v>不審ファイル、改ざん検知、バックドア、マルウェアスキャン、再感染、クリーンアップ</x:v>
+      </x:c>
       <x:c r="G32" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3324,28 +3334,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L32" s="16" t="str">
-        <x:v>WordPressのマルウェア感染チェックと駆除手順｜再感染を防ぐ視点</x:v>
+        <x:v>WordPressマルウェア感染の確認・駆除手順</x:v>
       </x:c>
       <x:c r="M32" s="16" t="str">
         <x:v>wordpress-malware-removal</x:v>
       </x:c>
       <x:c r="N32" s="16" t="str">
-        <x:v>WordPressのマルウェア感染チェックと駆除手順をテーマに、再感染を防ぐ視点ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WordPressのマルウェア感染を、不審ファイル、管理者追加、リダイレクト、検索結果の異常から確認します。駆除だけで終わらせず、侵入口の修正と再感染確認まで進められます。クリーンな状態の確認基準も示します。</x:v>
       </x:c>
       <x:c r="O32" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>7,000字</x:v>
       </x:c>
       <x:c r="P32" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="Q32" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="R32" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 脆弱性と攻撃</x:v>
       </x:c>
       <x:c r="S32" s="14" t="str">
-        <x:v>WordPress、セキュリティ、インシデント対応</x:v>
+        <x:v>マルウェア対策、インシデント対応、脆弱性管理</x:v>
       </x:c>
       <x:c r="T32" s="14" t="str">
         <x:v>01,32</x:v>
@@ -3360,7 +3370,7 @@
         <x:v>033.png</x:v>
       </x:c>
       <x:c r="X32" s="14" t="str">
-        <x:v>WordPressのマルウェア感染チェックと駆除手順｜再感染を防ぐ視点</x:v>
+        <x:v>WordPressマルウェア感染の確認・駆除手順</x:v>
       </x:c>
       <x:c r="Y32" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3374,15 +3384,15 @@
       <x:c r="AB32" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC32" s="16" t="str"/>
-      <x:c r="AD32" s="16" t="str"/>
-      <x:c r="AE32" s="16" t="str"/>
-      <x:c r="AF32" s="16" t="str"/>
-      <x:c r="AG32" s="16" t="str"/>
-      <x:c r="AH32" s="16" t="str"/>
-      <x:c r="AI32" s="16" t="str"/>
-      <x:c r="AJ32" s="14" t="str"/>
-      <x:c r="AK32" s="14" t="str"/>
+      <x:c r="AC32" s="16"/>
+      <x:c r="AD32" s="16"/>
+      <x:c r="AE32" s="16"/>
+      <x:c r="AF32" s="16"/>
+      <x:c r="AG32" s="16"/>
+      <x:c r="AH32" s="16"/>
+      <x:c r="AI32" s="16"/>
+      <x:c r="AJ32" s="14"/>
+      <x:c r="AK32" s="14"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="n">
@@ -3401,7 +3411,7 @@
         <x:v>wordpress ログイン画面 セキュリティ</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>wordpress ログイン画面 セキュリティ</x:v>
+        <x:v>ログインURL変更、wp-login.php、総当たり攻撃、404、プラグイン競合、復旧</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
         <x:v>10</x:v>
@@ -3419,28 +3429,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L33" s="16" t="str">
-        <x:v>WordPressのログイン画面URLは変更すべきか｜効果と副作用</x:v>
+        <x:v>WordPressログイン画面セキュリティ｜URL変更の効果</x:v>
       </x:c>
       <x:c r="M33" s="16" t="str">
         <x:v>change-wordpress-login-url</x:v>
       </x:c>
       <x:c r="N33" s="16" t="str">
-        <x:v>WordPressのログイン画面URLは変更すべきかをテーマに、効果と副作用ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress ログイン画面 セキュリティでURL変更が防げる攻撃と、防げない攻撃を区別します。アクセス減少の効果、互換性、URLを忘れた場合の復旧まで確認し、導入可否を決められます。変更しない選択肢も含めて検討できます。</x:v>
       </x:c>
       <x:c r="O33" s="16" t="str">
-        <x:v>6,000字</x:v>
+        <x:v>4,500字</x:v>
       </x:c>
       <x:c r="P33" s="16" t="n">
-        <x:v>5820</x:v>
+        <x:v>3825</x:v>
       </x:c>
       <x:c r="Q33" s="16" t="n">
-        <x:v>6180</x:v>
+        <x:v>5850</x:v>
       </x:c>
       <x:c r="R33" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; ログインと管理画面</x:v>
       </x:c>
       <x:c r="S33" s="14" t="str">
-        <x:v>WordPress、セキュリティ、ログイン対策</x:v>
+        <x:v>ログイン防御、セキュリティプラグイン、攻撃対策</x:v>
       </x:c>
       <x:c r="T33" s="14" t="str">
         <x:v>01,35,38</x:v>
@@ -3455,7 +3465,7 @@
         <x:v>036.png</x:v>
       </x:c>
       <x:c r="X33" s="14" t="str">
-        <x:v>WordPressのログイン画面URLは変更すべきか｜効果と副作用</x:v>
+        <x:v>WordPressログイン画面セキュリティ｜URL変更の効果</x:v>
       </x:c>
       <x:c r="Y33" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3469,15 +3479,15 @@
       <x:c r="AB33" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC33" s="16" t="str"/>
-      <x:c r="AD33" s="16" t="str"/>
-      <x:c r="AE33" s="16" t="str"/>
-      <x:c r="AF33" s="16" t="str"/>
-      <x:c r="AG33" s="16" t="str"/>
-      <x:c r="AH33" s="16" t="str"/>
-      <x:c r="AI33" s="16" t="str"/>
-      <x:c r="AJ33" s="14" t="str"/>
-      <x:c r="AK33" s="14" t="str"/>
+      <x:c r="AC33" s="16"/>
+      <x:c r="AD33" s="16"/>
+      <x:c r="AE33" s="16"/>
+      <x:c r="AF33" s="16"/>
+      <x:c r="AG33" s="16"/>
+      <x:c r="AH33" s="16"/>
+      <x:c r="AI33" s="16"/>
+      <x:c r="AJ33" s="14"/>
+      <x:c r="AK33" s="14"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="n">
@@ -3496,7 +3506,7 @@
         <x:v>wordpress 管理画面 セキュリティ</x:v>
       </x:c>
       <x:c r="F34" s="14" t="str">
-        <x:v>wordpress 管理画面 セキュリティ / wordpress 管理画面 セキュリティ対策</x:v>
+        <x:v>IP制限、BASIC認証、VPN、アクセス制御、固定IP、管理者権限</x:v>
       </x:c>
       <x:c r="G34" s="16" t="n">
         <x:v>10</x:v>
@@ -3514,28 +3524,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L34" s="16" t="str">
-        <x:v>WordPress管理画面のセキュリティ対策｜IP制限・BASIC認証の実装</x:v>
+        <x:v>WordPress管理画面セキュリティ｜IP制限と認証</x:v>
       </x:c>
       <x:c r="M34" s="16" t="str">
         <x:v>wordpress-admin-security</x:v>
       </x:c>
       <x:c r="N34" s="16" t="str">
-        <x:v>WordPress管理画面のセキュリティ対策をテーマに、IP制限・BASIC認証の実装ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress 管理画面 セキュリティを、IP制限、BASIC認証、VPN、権限管理で強化します。固定IPを使えない環境や外部担当者がいる場合も含め、現実的なアクセス制御を選べます。運用人数に合う方式を選べます。</x:v>
       </x:c>
       <x:c r="O34" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P34" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q34" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R34" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; ログインと管理画面</x:v>
       </x:c>
       <x:c r="S34" s="14" t="str">
-        <x:v>WordPress、セキュリティ、ログイン対策</x:v>
+        <x:v>ログイン防御、WAF・サーバー、設定監査</x:v>
       </x:c>
       <x:c r="T34" s="14" t="str">
         <x:v>01,35,38</x:v>
@@ -3550,7 +3560,7 @@
         <x:v>037.png</x:v>
       </x:c>
       <x:c r="X34" s="14" t="str">
-        <x:v>WordPress管理画面のセキュリティ対策｜IP制限・BASIC認証の実装</x:v>
+        <x:v>WordPress管理画面セキュリティ｜IP制限と認証</x:v>
       </x:c>
       <x:c r="Y34" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3564,15 +3574,15 @@
       <x:c r="AB34" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC34" s="16" t="str"/>
-      <x:c r="AD34" s="16" t="str"/>
-      <x:c r="AE34" s="16" t="str"/>
-      <x:c r="AF34" s="16" t="str"/>
-      <x:c r="AG34" s="16" t="str"/>
-      <x:c r="AH34" s="16" t="str"/>
-      <x:c r="AI34" s="16" t="str"/>
-      <x:c r="AJ34" s="14" t="str"/>
-      <x:c r="AK34" s="14" t="str"/>
+      <x:c r="AC34" s="16"/>
+      <x:c r="AD34" s="16"/>
+      <x:c r="AE34" s="16"/>
+      <x:c r="AF34" s="16"/>
+      <x:c r="AG34" s="16"/>
+      <x:c r="AH34" s="16"/>
+      <x:c r="AI34" s="16"/>
+      <x:c r="AJ34" s="14"/>
+      <x:c r="AK34" s="14"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="n">
@@ -3591,7 +3601,7 @@
         <x:v>wordpress 管理画面 ログイン セキュリティ</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>wordpress 管理画面 ログイン セキュリティ</x:v>
+        <x:v>二要素認証、認証アプリ、バックアップコード、管理者アカウント、復旧、共有アカウント</x:v>
       </x:c>
       <x:c r="G35" s="16" t="n">
         <x:v>10</x:v>
@@ -3609,28 +3619,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L35" s="16" t="str">
-        <x:v>WordPressに二要素認証を導入する方法｜運用負荷と復旧手順</x:v>
+        <x:v>WordPress管理画面ログインセキュリティ｜二要素認証</x:v>
       </x:c>
       <x:c r="M35" s="16" t="str">
         <x:v>wordpress-two-factor-authentication</x:v>
       </x:c>
       <x:c r="N35" s="16" t="str">
-        <x:v>WordPressに二要素認証を導入する方法をテーマに、運用負荷と復旧手順ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress 管理画面 ログイン セキュリティを二要素認証で強化する手順を示します。認証アプリ、バックアップコード、端末紛失時の復旧を整え、管理者を締め出さずに導入できます。復旧用コードの管理方法も分かります。</x:v>
       </x:c>
       <x:c r="O35" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P35" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q35" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R35" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; ログインと管理画面</x:v>
       </x:c>
       <x:c r="S35" s="14" t="str">
-        <x:v>WordPress、セキュリティ、ログイン対策</x:v>
+        <x:v>ログイン防御、セキュリティプラグイン、基本対策</x:v>
       </x:c>
       <x:c r="T35" s="14" t="str">
         <x:v>01,35</x:v>
@@ -3645,7 +3655,7 @@
         <x:v>038.png</x:v>
       </x:c>
       <x:c r="X35" s="14" t="str">
-        <x:v>WordPressに二要素認証を導入する方法｜運用負荷と復旧手順</x:v>
+        <x:v>WordPress管理画面ログインセキュリティ｜二要素認証</x:v>
       </x:c>
       <x:c r="Y35" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3659,15 +3669,15 @@
       <x:c r="AB35" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC35" s="16" t="str"/>
-      <x:c r="AD35" s="16" t="str"/>
-      <x:c r="AE35" s="16" t="str"/>
-      <x:c r="AF35" s="16" t="str"/>
-      <x:c r="AG35" s="16" t="str"/>
-      <x:c r="AH35" s="16" t="str"/>
-      <x:c r="AI35" s="16" t="str"/>
-      <x:c r="AJ35" s="14" t="str"/>
-      <x:c r="AK35" s="14" t="str"/>
+      <x:c r="AC35" s="16"/>
+      <x:c r="AD35" s="16"/>
+      <x:c r="AE35" s="16"/>
+      <x:c r="AF35" s="16"/>
+      <x:c r="AG35" s="16"/>
+      <x:c r="AH35" s="16"/>
+      <x:c r="AI35" s="16"/>
+      <x:c r="AJ35" s="14"/>
+      <x:c r="AK35" s="14"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="n">
@@ -3686,7 +3696,7 @@
         <x:v>xserver wordpress セキュリティ</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>xserver wordpress セキュリティ / xserver wordpress セキュリティ対策 / xserver wordpress セキュリティ 設定 / エックス サーバー wordpress セキュリティ / エックス サーバー wordpress セキュリティ 設定 / x サーバー wordpress セキュリティ / xserver wordpress セキュリティ プラグ イン</x:v>
+        <x:v>WAF設定、国外IP制限、ログイン試行制限、Web改ざん検知、SSL、バックアップ</x:v>
       </x:c>
       <x:c r="G36" s="16" t="n">
         <x:v>10</x:v>
@@ -3704,28 +3714,28 @@
         <x:v>単独／サーバー別は#41に集約</x:v>
       </x:c>
       <x:c r="L36" s="16" t="str">
-        <x:v>エックスサーバーのWordPressセキュリティ設定｜標準機能の範囲と限界</x:v>
+        <x:v>XserverのWordPressセキュリティ設定</x:v>
       </x:c>
       <x:c r="M36" s="16" t="str">
         <x:v>xserver-wordpress-security</x:v>
       </x:c>
       <x:c r="N36" s="16" t="str">
-        <x:v>エックスサーバーのWordPressセキュリティ設定をテーマに、標準機能の範囲と限界ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>xserver wordpress セキュリティで使えるWAF、国外IP制限、ログイン試行制限、SSL、バックアップを確認します。標準機能で守れる範囲と、WordPress側で補う設定を切り分けられます。</x:v>
       </x:c>
       <x:c r="O36" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P36" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q36" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R36" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S36" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サーバーセキュリティ</x:v>
+        <x:v>WAF・サーバー、基本対策、バックアップ</x:v>
       </x:c>
       <x:c r="T36" s="14" t="str">
         <x:v>01,40,46</x:v>
@@ -3740,7 +3750,7 @@
         <x:v>041.png</x:v>
       </x:c>
       <x:c r="X36" s="14" t="str">
-        <x:v>エックスサーバーのWordPressセキュリティ設定｜標準機能の範囲と限界</x:v>
+        <x:v>XserverのWordPressセキュリティ設定</x:v>
       </x:c>
       <x:c r="Y36" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3754,15 +3764,15 @@
       <x:c r="AB36" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC36" s="16" t="str"/>
-      <x:c r="AD36" s="16" t="str"/>
-      <x:c r="AE36" s="16" t="str"/>
-      <x:c r="AF36" s="16" t="str"/>
-      <x:c r="AG36" s="16" t="str"/>
-      <x:c r="AH36" s="16" t="str"/>
-      <x:c r="AI36" s="16" t="str"/>
-      <x:c r="AJ36" s="14" t="str"/>
-      <x:c r="AK36" s="14" t="str"/>
+      <x:c r="AC36" s="16"/>
+      <x:c r="AD36" s="16"/>
+      <x:c r="AE36" s="16"/>
+      <x:c r="AF36" s="16"/>
+      <x:c r="AG36" s="16"/>
+      <x:c r="AH36" s="16"/>
+      <x:c r="AI36" s="16"/>
+      <x:c r="AJ36" s="14"/>
+      <x:c r="AK36" s="14"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="16" t="n">
@@ -3781,7 +3791,7 @@
         <x:v>ロリポップ wordpress セキュリティ</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>ロリポップ wordpress セキュリティ</x:v>
+        <x:v>WAF誤検知、アクセス制限、独自SSL、バックアップ、FTP、PHP設定</x:v>
       </x:c>
       <x:c r="G37" s="16" t="n">
         <x:v>10</x:v>
@@ -3799,28 +3809,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L37" s="16" t="str">
-        <x:v>ロリポップでのWordPressセキュリティ設定｜WAF誤検知の対処込み</x:v>
+        <x:v>ロリポップWordPressセキュリティ｜WAF設定</x:v>
       </x:c>
       <x:c r="M37" s="16" t="str">
         <x:v>lolipop-wordpress-security</x:v>
       </x:c>
       <x:c r="N37" s="16" t="str">
-        <x:v>ロリポップでのWordPressセキュリティ設定をテーマに、WAF誤検知の対処込みための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>ロリポップ wordpress セキュリティのWAF、独自SSL、アクセス制限、バックアップを確認します。403エラーが出た際の誤検知切り分けも押さえ、機能を止めずに調整できます。管理画面での確認場所も把握できます。</x:v>
       </x:c>
       <x:c r="O37" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P37" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q37" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R37" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S37" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サーバーセキュリティ</x:v>
+        <x:v>WAF・サーバー、バックアップ、設定監査</x:v>
       </x:c>
       <x:c r="T37" s="14" t="str">
         <x:v>01,40,46</x:v>
@@ -3835,7 +3845,7 @@
         <x:v>044.png</x:v>
       </x:c>
       <x:c r="X37" s="14" t="str">
-        <x:v>ロリポップでのWordPressセキュリティ設定｜WAF誤検知の対処込み</x:v>
+        <x:v>ロリポップWordPressセキュリティ｜WAF設定</x:v>
       </x:c>
       <x:c r="Y37" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3849,15 +3859,15 @@
       <x:c r="AB37" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC37" s="16" t="str"/>
-      <x:c r="AD37" s="16" t="str"/>
-      <x:c r="AE37" s="16" t="str"/>
-      <x:c r="AF37" s="16" t="str"/>
-      <x:c r="AG37" s="16" t="str"/>
-      <x:c r="AH37" s="16" t="str"/>
-      <x:c r="AI37" s="16" t="str"/>
-      <x:c r="AJ37" s="14" t="str"/>
-      <x:c r="AK37" s="14" t="str"/>
+      <x:c r="AC37" s="16"/>
+      <x:c r="AD37" s="16"/>
+      <x:c r="AE37" s="16"/>
+      <x:c r="AF37" s="16"/>
+      <x:c r="AG37" s="16"/>
+      <x:c r="AH37" s="16"/>
+      <x:c r="AI37" s="16"/>
+      <x:c r="AJ37" s="14"/>
+      <x:c r="AK37" s="14"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="16" t="n">
@@ -3876,7 +3886,7 @@
         <x:v>lightsail wordpress セキュリティ</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>lightsail wordpress セキュリティ</x:v>
+        <x:v>ファイアウォール、SSH、固定IP、スナップショット、Bitnami、アップデート</x:v>
       </x:c>
       <x:c r="G38" s="16" t="n">
         <x:v>10</x:v>
@@ -3894,28 +3904,28 @@
         <x:v>単独／難易度21は狙い目</x:v>
       </x:c>
       <x:c r="L38" s="16" t="str">
-        <x:v>AWS LightsailのWordPressセキュリティ｜自己管理環境で必要な設定</x:v>
+        <x:v>Lightsail WordPressセキュリティ設定</x:v>
       </x:c>
       <x:c r="M38" s="16" t="str">
         <x:v>aws-lightsail-wordpress-security</x:v>
       </x:c>
       <x:c r="N38" s="16" t="str">
-        <x:v>AWS LightsailのWordPressセキュリティをテーマに、自己管理環境で必要な設定ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>lightsail wordpress セキュリティで必要なファイアウォール、SSH、固定IP、OS更新、スナップショットを整理します。自己管理となる範囲を把握し、初期構築後の作業漏れを防げます。月次保守の項目にも落とし込めます。</x:v>
       </x:c>
       <x:c r="O38" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P38" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q38" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R38" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S38" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サーバーセキュリティ</x:v>
+        <x:v>WAF・サーバー、アップデート運用、バックアップ</x:v>
       </x:c>
       <x:c r="T38" s="14" t="str">
         <x:v>01,40,46</x:v>
@@ -3930,7 +3940,7 @@
         <x:v>045.png</x:v>
       </x:c>
       <x:c r="X38" s="14" t="str">
-        <x:v>AWS LightsailのWordPressセキュリティ｜自己管理環境で必要な設定</x:v>
+        <x:v>Lightsail WordPressセキュリティ設定</x:v>
       </x:c>
       <x:c r="Y38" s="16" t="str">
         <x:v>未着手</x:v>
@@ -3944,15 +3954,15 @@
       <x:c r="AB38" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC38" s="16" t="str"/>
-      <x:c r="AD38" s="16" t="str"/>
-      <x:c r="AE38" s="16" t="str"/>
-      <x:c r="AF38" s="16" t="str"/>
-      <x:c r="AG38" s="16" t="str"/>
-      <x:c r="AH38" s="16" t="str"/>
-      <x:c r="AI38" s="16" t="str"/>
-      <x:c r="AJ38" s="14" t="str"/>
-      <x:c r="AK38" s="14" t="str"/>
+      <x:c r="AC38" s="16"/>
+      <x:c r="AD38" s="16"/>
+      <x:c r="AE38" s="16"/>
+      <x:c r="AF38" s="16"/>
+      <x:c r="AG38" s="16"/>
+      <x:c r="AH38" s="16"/>
+      <x:c r="AI38" s="16"/>
+      <x:c r="AJ38" s="14"/>
+      <x:c r="AK38" s="14"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="16" t="n">
@@ -3967,9 +3977,9 @@
       <x:c r="D39" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E39" s="14" t="str"/>
+      <x:c r="E39" s="14"/>
       <x:c r="F39" s="14" t="str">
-        <x:v>さくら wordpress セキュリティ</x:v>
+        <x:v>WAF、無料SSL、自動バックアップ、改ざん検知、国外IP制限、復元</x:v>
       </x:c>
       <x:c r="G39" s="16" t="n">
         <x:v>0</x:v>
@@ -3987,28 +3997,28 @@
         <x:v>見送り→#46比較表に内包（検索数0）</x:v>
       </x:c>
       <x:c r="L39" s="16" t="str">
-        <x:v>WordPress向けレンタルサーバーのセキュリティ機能比較｜主要5社を横比較</x:v>
+        <x:v>WordPressレンタルサーバー5社の機能比較</x:v>
       </x:c>
       <x:c r="M39" s="16" t="str">
         <x:v>wordpress-hosting-security-comparison</x:v>
       </x:c>
       <x:c r="N39" s="16" t="str">
-        <x:v>WordPress向けレンタルサーバーのセキュリティ機能比較をテーマに、主要5社を横比較ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WordPress向けレンタルサーバー5社を、WAF、無料SSL、自動バックアップ、改ざん検知、国外IP制限で比較します。料金だけでは見えない保護機能と復旧条件から候補を選べます。契約前の比較表として活用できます。</x:v>
       </x:c>
       <x:c r="O39" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>7,000字</x:v>
       </x:c>
       <x:c r="P39" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="Q39" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="R39" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S39" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サーバーセキュリティ</x:v>
+        <x:v>WAF・サーバー、バックアップ、基本対策</x:v>
       </x:c>
       <x:c r="T39" s="14" t="str">
         <x:v>01,40</x:v>
@@ -4023,7 +4033,7 @@
         <x:v>046.png</x:v>
       </x:c>
       <x:c r="X39" s="14" t="str">
-        <x:v>WordPress向けレンタルサーバーのセキュリティ機能比較｜主要5社を横比較</x:v>
+        <x:v>WordPressレンタルサーバー5社の機能比較</x:v>
       </x:c>
       <x:c r="Y39" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4037,15 +4047,15 @@
       <x:c r="AB39" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC39" s="16" t="str"/>
-      <x:c r="AD39" s="16" t="str"/>
-      <x:c r="AE39" s="16" t="str"/>
-      <x:c r="AF39" s="16" t="str"/>
-      <x:c r="AG39" s="16" t="str"/>
-      <x:c r="AH39" s="16" t="str"/>
-      <x:c r="AI39" s="16" t="str"/>
-      <x:c r="AJ39" s="14" t="str"/>
-      <x:c r="AK39" s="14" t="str"/>
+      <x:c r="AC39" s="16"/>
+      <x:c r="AD39" s="16"/>
+      <x:c r="AE39" s="16"/>
+      <x:c r="AF39" s="16"/>
+      <x:c r="AG39" s="16"/>
+      <x:c r="AH39" s="16"/>
+      <x:c r="AI39" s="16"/>
+      <x:c r="AJ39" s="14"/>
+      <x:c r="AK39" s="14"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="16" t="n">
@@ -4064,7 +4074,7 @@
         <x:v>wordpress ecサイト セキュリティ</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>wordpress ecサイト セキュリティ</x:v>
+        <x:v>WooCommerce、決済代行、PCI DSS、顧客情報、管理者権限、不正注文</x:v>
       </x:c>
       <x:c r="G40" s="16" t="n">
         <x:v>10</x:v>
@@ -4082,28 +4092,28 @@
         <x:v>単独／単価が高い</x:v>
       </x:c>
       <x:c r="L40" s="16" t="str">
-        <x:v>WooCommerceなどWordPress ECサイトのセキュリティ｜決済情報を守る要件</x:v>
+        <x:v>WordPress ECサイトセキュリティ｜決済と個人情報</x:v>
       </x:c>
       <x:c r="M40" s="16" t="str">
         <x:v>woocommerce-security</x:v>
       </x:c>
       <x:c r="N40" s="16" t="str">
-        <x:v>WooCommerceなどWordPress ECサイトのセキュリティをテーマに、決済情報を守る要件ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress ecサイト セキュリティを、決済情報、顧客情報、管理者権限、拡張機能の4点で確認します。WooCommerceで保持する情報を整理し、外部決済へ任せる範囲を決められます。決済代行との責任分担も明確になります。</x:v>
       </x:c>
       <x:c r="O40" s="16" t="str">
-        <x:v>10,000字</x:v>
+        <x:v>7,500字</x:v>
       </x:c>
       <x:c r="P40" s="16" t="n">
-        <x:v>9700</x:v>
+        <x:v>6375</x:v>
       </x:c>
       <x:c r="Q40" s="16" t="n">
-        <x:v>10300</x:v>
+        <x:v>9750</x:v>
       </x:c>
       <x:c r="R40" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 用途別（EC・会員サイト・社内利用）</x:v>
       </x:c>
       <x:c r="S40" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サイト設計</x:v>
+        <x:v>個人情報保護、基本対策、セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="T40" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4118,7 +4128,7 @@
         <x:v>047.png</x:v>
       </x:c>
       <x:c r="X40" s="14" t="str">
-        <x:v>WooCommerceなどWordPress ECサイトのセキュリティ｜決済情報を守る要件</x:v>
+        <x:v>WordPress ECサイトセキュリティ｜決済と個人情報</x:v>
       </x:c>
       <x:c r="Y40" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4132,15 +4142,15 @@
       <x:c r="AB40" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC40" s="16" t="str"/>
-      <x:c r="AD40" s="16" t="str"/>
-      <x:c r="AE40" s="16" t="str"/>
-      <x:c r="AF40" s="16" t="str"/>
-      <x:c r="AG40" s="16" t="str"/>
-      <x:c r="AH40" s="16" t="str"/>
-      <x:c r="AI40" s="16" t="str"/>
-      <x:c r="AJ40" s="14" t="str"/>
-      <x:c r="AK40" s="14" t="str"/>
+      <x:c r="AC40" s="16"/>
+      <x:c r="AD40" s="16"/>
+      <x:c r="AE40" s="16"/>
+      <x:c r="AF40" s="16"/>
+      <x:c r="AG40" s="16"/>
+      <x:c r="AH40" s="16"/>
+      <x:c r="AI40" s="16"/>
+      <x:c r="AJ40" s="14"/>
+      <x:c r="AK40" s="14"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="16" t="n">
@@ -4159,7 +4169,7 @@
         <x:v>wordpress 会員サイト セキュリティ</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>wordpress 会員サイト セキュリティ</x:v>
+        <x:v>個人情報、アクセス権限、パスワード再設定、退会処理、ログ監査、バックアップ</x:v>
       </x:c>
       <x:c r="G41" s="16" t="n">
         <x:v>10</x:v>
@@ -4177,28 +4187,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L41" s="16" t="str">
-        <x:v>WordPress会員サイトのセキュリティ設計｜個人情報を扱う前提の対策</x:v>
+        <x:v>WordPress会員サイトセキュリティ｜設計要件</x:v>
       </x:c>
       <x:c r="M41" s="16" t="str">
         <x:v>wordpress-membership-site-security</x:v>
       </x:c>
       <x:c r="N41" s="16" t="str">
-        <x:v>WordPress会員サイトのセキュリティ設計をテーマに、個人情報を扱う前提の対策ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress 会員サイト セキュリティで必要な権限分離、パスワード再設定、退会処理、操作ログ、バックアップを整理します。保存する個人情報を減らし、運用開始前の要件を固められます。利用規約と運用手順へ反映できます。</x:v>
       </x:c>
       <x:c r="O41" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>7,000字</x:v>
       </x:c>
       <x:c r="P41" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5950</x:v>
       </x:c>
       <x:c r="Q41" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>9100</x:v>
       </x:c>
       <x:c r="R41" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 用途別（EC・会員サイト・社内利用）</x:v>
       </x:c>
       <x:c r="S41" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サイト設計</x:v>
+        <x:v>個人情報保護、ログイン防御、バックアップ</x:v>
       </x:c>
       <x:c r="T41" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4213,7 +4223,7 @@
         <x:v>048.png</x:v>
       </x:c>
       <x:c r="X41" s="14" t="str">
-        <x:v>WordPress会員サイトのセキュリティ設計｜個人情報を扱う前提の対策</x:v>
+        <x:v>WordPress会員サイトセキュリティ｜設計要件</x:v>
       </x:c>
       <x:c r="Y41" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4227,15 +4237,15 @@
       <x:c r="AB41" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC41" s="16" t="str"/>
-      <x:c r="AD41" s="16" t="str"/>
-      <x:c r="AE41" s="16" t="str"/>
-      <x:c r="AF41" s="16" t="str"/>
-      <x:c r="AG41" s="16" t="str"/>
-      <x:c r="AH41" s="16" t="str"/>
-      <x:c r="AI41" s="16" t="str"/>
-      <x:c r="AJ41" s="14" t="str"/>
-      <x:c r="AK41" s="14" t="str"/>
+      <x:c r="AC41" s="16"/>
+      <x:c r="AD41" s="16"/>
+      <x:c r="AE41" s="16"/>
+      <x:c r="AF41" s="16"/>
+      <x:c r="AG41" s="16"/>
+      <x:c r="AH41" s="16"/>
+      <x:c r="AI41" s="16"/>
+      <x:c r="AJ41" s="14"/>
+      <x:c r="AK41" s="14"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="16" t="n">
@@ -4254,7 +4264,7 @@
         <x:v>wordpress 社内ポータル セキュリティ</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>wordpress 社内ポータル セキュリティ</x:v>
+        <x:v>社内認証、VPN、アクセス制限、退職者アカウント、権限管理、監査ログ</x:v>
       </x:c>
       <x:c r="G42" s="16" t="n">
         <x:v>10</x:v>
@@ -4272,28 +4282,28 @@
         <x:v>単独／実務知見で勝てる</x:v>
       </x:c>
       <x:c r="L42" s="16" t="str">
-        <x:v>WordPressを社内ポータルで使う際のセキュリティ要件</x:v>
+        <x:v>WordPress社内ポータルセキュリティ｜運用要件</x:v>
       </x:c>
       <x:c r="M42" s="16" t="str">
         <x:v>wordpress-intranet-security</x:v>
       </x:c>
       <x:c r="N42" s="16" t="str">
-        <x:v>WordPressを社内ポータルで使う際のセキュリティ要件について、必要な設定、判断基準、注意点を実務目線で解説します。WordPress運用者が迷いやすい点を整理し、次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress 社内ポータル セキュリティを、接続元制限、認証、権限、退職者処理、監査ログで設計します。インターネット公開の要否を見直し、社内利用に必要な統制を決められます。外部公開する場合の追加策も分かります。</x:v>
       </x:c>
       <x:c r="O42" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P42" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q42" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R42" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 用途別（EC・会員サイト・社内利用）</x:v>
       </x:c>
       <x:c r="S42" s="14" t="str">
-        <x:v>WordPress、セキュリティ、サイト設計</x:v>
+        <x:v>個人情報保護、ログイン防御、設定監査</x:v>
       </x:c>
       <x:c r="T42" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4308,7 +4318,7 @@
         <x:v>049.png</x:v>
       </x:c>
       <x:c r="X42" s="14" t="str">
-        <x:v>WordPressを社内ポータルで使う際のセキュリティ要件</x:v>
+        <x:v>WordPress社内ポータルセキュリティ｜運用要件</x:v>
       </x:c>
       <x:c r="Y42" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4322,15 +4332,15 @@
       <x:c r="AB42" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC42" s="16" t="str"/>
-      <x:c r="AD42" s="16" t="str"/>
-      <x:c r="AE42" s="16" t="str"/>
-      <x:c r="AF42" s="16" t="str"/>
-      <x:c r="AG42" s="16" t="str"/>
-      <x:c r="AH42" s="16" t="str"/>
-      <x:c r="AI42" s="16" t="str"/>
-      <x:c r="AJ42" s="14" t="str"/>
-      <x:c r="AK42" s="14" t="str"/>
+      <x:c r="AC42" s="16"/>
+      <x:c r="AD42" s="16"/>
+      <x:c r="AE42" s="16"/>
+      <x:c r="AF42" s="16"/>
+      <x:c r="AG42" s="16"/>
+      <x:c r="AH42" s="16"/>
+      <x:c r="AI42" s="16"/>
+      <x:c r="AJ42" s="14"/>
+      <x:c r="AK42" s="14"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="16" t="n">
@@ -4349,7 +4359,7 @@
         <x:v>wordpress テーマ セキュリティ</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>wordpress テーマ 自作 セキュリティ / wordpress テーマ セキュリティ</x:v>
+        <x:v>公式ディレクトリ、更新履歴、子テーマ、エスケープ、nonce、サポート終了</x:v>
       </x:c>
       <x:c r="G43" s="16" t="n">
         <x:v>10</x:v>
@@ -4367,28 +4377,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L43" s="16" t="str">
-        <x:v>WordPressテーマのセキュリティ｜配布テーマの見極めと自作時の注意点</x:v>
+        <x:v>WordPressテーマセキュリティ｜選定と自作</x:v>
       </x:c>
       <x:c r="M43" s="16" t="str">
         <x:v>wordpress-theme-security</x:v>
       </x:c>
       <x:c r="N43" s="16" t="str">
-        <x:v>WordPressテーマのセキュリティをテーマに、配布テーマの見極めと自作時の注意点ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress テーマ セキュリティを、配布元、更新履歴、サポート、不要機能、自作コードの5点で確認します。公式テーマを選ぶ基準と、出力エスケープなど実装時の注意を判断できます。配布前のコード確認にも役立ちます。</x:v>
       </x:c>
       <x:c r="O43" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P43" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q43" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R43" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S43" s="14" t="str">
-        <x:v>WordPress、セキュリティ、WordPress設定</x:v>
+        <x:v>API・開発、脆弱性管理、アップデート運用</x:v>
       </x:c>
       <x:c r="T43" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4403,7 +4413,7 @@
         <x:v>050.png</x:v>
       </x:c>
       <x:c r="X43" s="14" t="str">
-        <x:v>WordPressテーマのセキュリティ｜配布テーマの見極めと自作時の注意点</x:v>
+        <x:v>WordPressテーマセキュリティ｜選定と自作</x:v>
       </x:c>
       <x:c r="Y43" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4417,15 +4427,15 @@
       <x:c r="AB43" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC43" s="16" t="str"/>
-      <x:c r="AD43" s="16" t="str"/>
-      <x:c r="AE43" s="16" t="str"/>
-      <x:c r="AF43" s="16" t="str"/>
-      <x:c r="AG43" s="16" t="str"/>
-      <x:c r="AH43" s="16" t="str"/>
-      <x:c r="AI43" s="16" t="str"/>
-      <x:c r="AJ43" s="14" t="str"/>
-      <x:c r="AK43" s="14" t="str"/>
+      <x:c r="AC43" s="16"/>
+      <x:c r="AD43" s="16"/>
+      <x:c r="AE43" s="16"/>
+      <x:c r="AF43" s="16"/>
+      <x:c r="AG43" s="16"/>
+      <x:c r="AH43" s="16"/>
+      <x:c r="AI43" s="16"/>
+      <x:c r="AJ43" s="14"/>
+      <x:c r="AK43" s="14"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="16" t="n">
@@ -4444,7 +4454,7 @@
         <x:v>wordpress rest api セキュリティ</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>wordpress rest api セキュリティ</x:v>
+        <x:v>エンドポイント、認証、ユーザー列挙、権限チェック、Application Passwords、無効化</x:v>
       </x:c>
       <x:c r="G44" s="16" t="n">
         <x:v>10</x:v>
@@ -4462,28 +4472,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L44" s="16" t="str">
-        <x:v>WordPress REST APIのセキュリティ｜露出制御と無効化の判断</x:v>
+        <x:v>WordPress REST APIセキュリティ｜公開範囲の判断</x:v>
       </x:c>
       <x:c r="M44" s="16" t="str">
         <x:v>wordpress-rest-api-security</x:v>
       </x:c>
       <x:c r="N44" s="16" t="str">
-        <x:v>WordPress REST APIのセキュリティをテーマに、露出制御と無効化の判断ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress rest api セキュリティを、公開エンドポイント、認証、権限確認、ユーザー情報の露出から点検します。全面無効化の副作用を避け、制限すべき範囲だけを決められます。連携機能を壊さない制御ができます。</x:v>
       </x:c>
       <x:c r="O44" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P44" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q44" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R44" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S44" s="14" t="str">
-        <x:v>WordPress、セキュリティ、WordPress設定</x:v>
+        <x:v>API・開発、設定監査、ログイン防御</x:v>
       </x:c>
       <x:c r="T44" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4498,7 +4508,7 @@
         <x:v>051.png</x:v>
       </x:c>
       <x:c r="X44" s="14" t="str">
-        <x:v>WordPress REST APIのセキュリティ｜露出制御と無効化の判断</x:v>
+        <x:v>WordPress REST APIセキュリティ｜公開範囲の判断</x:v>
       </x:c>
       <x:c r="Y44" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4512,15 +4522,15 @@
       <x:c r="AB44" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC44" s="16" t="str"/>
-      <x:c r="AD44" s="16" t="str"/>
-      <x:c r="AE44" s="16" t="str"/>
-      <x:c r="AF44" s="16" t="str"/>
-      <x:c r="AG44" s="16" t="str"/>
-      <x:c r="AH44" s="16" t="str"/>
-      <x:c r="AI44" s="16" t="str"/>
-      <x:c r="AJ44" s="14" t="str"/>
-      <x:c r="AK44" s="14" t="str"/>
+      <x:c r="AC44" s="16"/>
+      <x:c r="AD44" s="16"/>
+      <x:c r="AE44" s="16"/>
+      <x:c r="AF44" s="16"/>
+      <x:c r="AG44" s="16"/>
+      <x:c r="AH44" s="16"/>
+      <x:c r="AI44" s="16"/>
+      <x:c r="AJ44" s="14"/>
+      <x:c r="AK44" s="14"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="16" t="n">
@@ -4539,7 +4549,7 @@
         <x:v>wordpress セキュリティ ヘッダー</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>wordpress セキュリティ ヘッダー</x:v>
+        <x:v>Content-Security-Policy、Strict-Transport-Security、X-Frame-Options、Permissions-Policy、Report-Only、混在コンテンツ</x:v>
       </x:c>
       <x:c r="G45" s="16" t="n">
         <x:v>0</x:v>
@@ -4557,28 +4567,28 @@
         <x:v>保留／難易度16は最低。検索数0だがGEO・技術者向けに作成価値あり</x:v>
       </x:c>
       <x:c r="L45" s="16" t="str">
-        <x:v>WordPressのセキュリティヘッダー設定｜CSP・HSTS・X-Frame-Options</x:v>
+        <x:v>WordPressセキュリティヘッダー｜CSP・HSTS設定</x:v>
       </x:c>
       <x:c r="M45" s="16" t="str">
         <x:v>wordpress-security-headers</x:v>
       </x:c>
       <x:c r="N45" s="16" t="str">
-        <x:v>WordPressのセキュリティヘッダー設定をテーマに、CSP・HSTS・X-Frame-Optionsための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress セキュリティ ヘッダーとしてCSP、HSTS、X-Frame-Optionsを設定する順序を示します。Report-Onlyで影響を確認し、表示崩れや外部サービス停止を避けて導入できます。</x:v>
       </x:c>
       <x:c r="O45" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P45" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q45" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R45" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S45" s="14" t="str">
-        <x:v>WordPress、セキュリティ、WordPress設定</x:v>
+        <x:v>WAF・サーバー、API・開発、設定監査</x:v>
       </x:c>
       <x:c r="T45" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4593,7 +4603,7 @@
         <x:v>052.png</x:v>
       </x:c>
       <x:c r="X45" s="14" t="str">
-        <x:v>WordPressのセキュリティヘッダー設定｜CSP・HSTS・X-Frame-Options</x:v>
+        <x:v>WordPressセキュリティヘッダー｜CSP・HSTS設定</x:v>
       </x:c>
       <x:c r="Y45" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4607,15 +4617,15 @@
       <x:c r="AB45" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC45" s="16" t="str"/>
-      <x:c r="AD45" s="16" t="str"/>
-      <x:c r="AE45" s="16" t="str"/>
-      <x:c r="AF45" s="16" t="str"/>
-      <x:c r="AG45" s="16" t="str"/>
-      <x:c r="AH45" s="16" t="str"/>
-      <x:c r="AI45" s="16" t="str"/>
-      <x:c r="AJ45" s="14" t="str"/>
-      <x:c r="AK45" s="14" t="str"/>
+      <x:c r="AC45" s="16"/>
+      <x:c r="AD45" s="16"/>
+      <x:c r="AE45" s="16"/>
+      <x:c r="AF45" s="16"/>
+      <x:c r="AG45" s="16"/>
+      <x:c r="AH45" s="16"/>
+      <x:c r="AI45" s="16"/>
+      <x:c r="AJ45" s="14"/>
+      <x:c r="AK45" s="14"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="16" t="n">
@@ -4634,7 +4644,7 @@
         <x:v>wordpress contact form 7 セキュリティ</x:v>
       </x:c>
       <x:c r="F46" s="14" t="str">
-        <x:v>wordpress contact form 7 セキュリティ / wordpress フォーム セキュリティ / wordpress flamingo セキュリティ</x:v>
+        <x:v>Flamingo、reCAPTCHA、個人情報、メール送信、スパム、保存期間</x:v>
       </x:c>
       <x:c r="G46" s="16" t="n">
         <x:v>10</x:v>
@@ -4652,28 +4662,28 @@
         <x:v>単独</x:v>
       </x:c>
       <x:c r="L46" s="16" t="str">
-        <x:v>Contact Form 7のセキュリティ｜スパム対策とFlamingoの保存データ</x:v>
+        <x:v>WordPress Contact Form 7セキュリティ対策</x:v>
       </x:c>
       <x:c r="M46" s="16" t="str">
         <x:v>contact-form-7-security</x:v>
       </x:c>
       <x:c r="N46" s="16" t="str">
-        <x:v>Contact Form 7のセキュリティをテーマに、スパム対策とFlamingoの保存データための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>wordpress contact form 7 セキュリティを、スパム防止、送信先、Flamingoの保存データ、保存期間から確認します。問い合わせ情報を必要以上に残さず、運用に合う保護方法を選べます。</x:v>
       </x:c>
       <x:c r="O46" s="16" t="str">
-        <x:v>7,000字</x:v>
+        <x:v>5,500字</x:v>
       </x:c>
       <x:c r="P46" s="16" t="n">
-        <x:v>6790</x:v>
+        <x:v>4675</x:v>
       </x:c>
       <x:c r="Q46" s="16" t="n">
-        <x:v>7210</x:v>
+        <x:v>7150</x:v>
       </x:c>
       <x:c r="R46" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S46" s="14" t="str">
-        <x:v>WordPress、セキュリティ、WordPress設定</x:v>
+        <x:v>個人情報保護、API・開発、設定監査</x:v>
       </x:c>
       <x:c r="T46" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4688,7 +4698,7 @@
         <x:v>053.png</x:v>
       </x:c>
       <x:c r="X46" s="14" t="str">
-        <x:v>Contact Form 7のセキュリティ｜スパム対策とFlamingoの保存データ</x:v>
+        <x:v>WordPress Contact Form 7セキュリティ対策</x:v>
       </x:c>
       <x:c r="Y46" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4702,15 +4712,15 @@
       <x:c r="AB46" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC46" s="16" t="str"/>
-      <x:c r="AD46" s="16" t="str"/>
-      <x:c r="AE46" s="16" t="str"/>
-      <x:c r="AF46" s="16" t="str"/>
-      <x:c r="AG46" s="16" t="str"/>
-      <x:c r="AH46" s="16" t="str"/>
-      <x:c r="AI46" s="16" t="str"/>
-      <x:c r="AJ46" s="14" t="str"/>
-      <x:c r="AK46" s="14" t="str"/>
+      <x:c r="AC46" s="16"/>
+      <x:c r="AD46" s="16"/>
+      <x:c r="AE46" s="16"/>
+      <x:c r="AF46" s="16"/>
+      <x:c r="AG46" s="16"/>
+      <x:c r="AH46" s="16"/>
+      <x:c r="AI46" s="16"/>
+      <x:c r="AJ46" s="14"/>
+      <x:c r="AK46" s="14"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="16" t="n">
@@ -4725,8 +4735,10 @@
       <x:c r="D47" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E47" s="14" t="str"/>
-      <x:c r="F47" s="14" t="str"/>
+      <x:c r="E47" s="14"/>
+      <x:c r="F47" s="14" t="str">
+        <x:v>ログインページ変更、画像認証、ログインロック、更新通知、XML-RPC、除外設定</x:v>
+      </x:c>
       <x:c r="G47" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4743,28 +4755,28 @@
         <x:v>プラグイン個別</x:v>
       </x:c>
       <x:c r="L47" s="16" t="str">
-        <x:v>SiteGuard WP Pluginの設定方法｜推奨設定と注意点</x:v>
+        <x:v>SiteGuard WP Pluginの推奨設定と注意点</x:v>
       </x:c>
       <x:c r="M47" s="16" t="str">
         <x:v>siteguard-wp-plugin-settings</x:v>
       </x:c>
       <x:c r="N47" s="16" t="str">
-        <x:v>SiteGuard WP Pluginの設定方法をテーマに、推奨設定と注意点ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>SiteGuard WP Pluginのログインページ変更、画像認証、ログインロック、更新通知を順に設定します。管理者が入れなくなる条件と復旧方法も確認し、有効にする機能を選べます。設定変更前の準備も分かります。</x:v>
       </x:c>
       <x:c r="O47" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P47" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q47" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R47" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S47" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、ログイン防御、設定監査</x:v>
       </x:c>
       <x:c r="T47" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4779,7 +4791,7 @@
         <x:v>017.png</x:v>
       </x:c>
       <x:c r="X47" s="14" t="str">
-        <x:v>SiteGuard WP Pluginの設定方法｜推奨設定と注意点</x:v>
+        <x:v>SiteGuard WP Pluginの推奨設定と注意点</x:v>
       </x:c>
       <x:c r="Y47" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4793,15 +4805,15 @@
       <x:c r="AB47" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC47" s="16" t="str"/>
-      <x:c r="AD47" s="16" t="str"/>
-      <x:c r="AE47" s="16" t="str"/>
-      <x:c r="AF47" s="16" t="str"/>
-      <x:c r="AG47" s="16" t="str"/>
-      <x:c r="AH47" s="16" t="str"/>
-      <x:c r="AI47" s="16" t="str"/>
-      <x:c r="AJ47" s="14" t="str"/>
-      <x:c r="AK47" s="14" t="str"/>
+      <x:c r="AC47" s="16"/>
+      <x:c r="AD47" s="16"/>
+      <x:c r="AE47" s="16"/>
+      <x:c r="AF47" s="16"/>
+      <x:c r="AG47" s="16"/>
+      <x:c r="AH47" s="16"/>
+      <x:c r="AI47" s="16"/>
+      <x:c r="AJ47" s="14"/>
+      <x:c r="AK47" s="14"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="16" t="n">
@@ -4816,8 +4828,10 @@
       <x:c r="D48" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E48" s="14" t="str"/>
-      <x:c r="F48" s="14" t="str"/>
+      <x:c r="E48" s="14"/>
+      <x:c r="F48" s="14" t="str">
+        <x:v>AIOS、ログインロック、ファイアウォール、スキャン、二要素認証、バックアップ</x:v>
+      </x:c>
       <x:c r="G48" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4834,28 +4848,28 @@
         <x:v>プラグイン個別</x:v>
       </x:c>
       <x:c r="L48" s="16" t="str">
-        <x:v>All-In-One Security（AIOS）の使い方｜推奨設定とパフォーマンス影響</x:v>
+        <x:v>All-In-One Securityの推奨設定と負荷</x:v>
       </x:c>
       <x:c r="M48" s="16" t="str">
         <x:v>aios-settings-guide</x:v>
       </x:c>
       <x:c r="N48" s="16" t="str">
-        <x:v>All-In-One Security（AIOS）の使い方をテーマに、推奨設定とパフォーマンス影響ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>All-In-One Security（AIOS）のログイン保護、ファイアウォール、二要素認証、スキャンを確認します。機能の重複とサーバー負荷を見ながら、段階的に有効化する設定を決められます。有効化する順番も組み立てられます。</x:v>
       </x:c>
       <x:c r="O48" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P48" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q48" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R48" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S48" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、WAF・サーバー、ログイン防御</x:v>
       </x:c>
       <x:c r="T48" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4870,7 +4884,7 @@
         <x:v>018.png</x:v>
       </x:c>
       <x:c r="X48" s="14" t="str">
-        <x:v>All-In-One Security（AIOS）の使い方｜推奨設定とパフォーマンス影響</x:v>
+        <x:v>All-In-One Securityの推奨設定と負荷</x:v>
       </x:c>
       <x:c r="Y48" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4884,15 +4898,15 @@
       <x:c r="AB48" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC48" s="16" t="str"/>
-      <x:c r="AD48" s="16" t="str"/>
-      <x:c r="AE48" s="16" t="str"/>
-      <x:c r="AF48" s="16" t="str"/>
-      <x:c r="AG48" s="16" t="str"/>
-      <x:c r="AH48" s="16" t="str"/>
-      <x:c r="AI48" s="16" t="str"/>
-      <x:c r="AJ48" s="14" t="str"/>
-      <x:c r="AK48" s="14" t="str"/>
+      <x:c r="AC48" s="16"/>
+      <x:c r="AD48" s="16"/>
+      <x:c r="AE48" s="16"/>
+      <x:c r="AF48" s="16"/>
+      <x:c r="AG48" s="16"/>
+      <x:c r="AH48" s="16"/>
+      <x:c r="AI48" s="16"/>
+      <x:c r="AJ48" s="14"/>
+      <x:c r="AK48" s="14"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="16" t="n">
@@ -4907,8 +4921,10 @@
       <x:c r="D49" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E49" s="14" t="str"/>
-      <x:c r="F49" s="14" t="str"/>
+      <x:c r="E49" s="14"/>
+      <x:c r="F49" s="14" t="str">
+        <x:v>ファイアウォール、マルウェアスキャン、ログイン保護、二要素認証、ブロック、通知</x:v>
+      </x:c>
       <x:c r="G49" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4925,28 +4941,28 @@
         <x:v>プラグイン個別</x:v>
       </x:c>
       <x:c r="L49" s="16" t="str">
-        <x:v>Wordfenceの使い方と設定｜無料版でどこまで守れるか</x:v>
+        <x:v>Wordfence無料版の設定と機能範囲</x:v>
       </x:c>
       <x:c r="M49" s="16" t="str">
         <x:v>wordfence-settings-guide</x:v>
       </x:c>
       <x:c r="N49" s="16" t="str">
-        <x:v>Wordfenceの使い方と設定をテーマに、無料版でどこまで守れるかための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>Wordfence無料版のファイアウォール、マルウェアスキャン、二要素認証、通知設定を確認します。有料版との差が運用へ与える影響を整理し、無料版で足りるサイトか判断できます。導入後の監視項目も把握できます。</x:v>
       </x:c>
       <x:c r="O49" s="16" t="str">
-        <x:v>9,000字</x:v>
+        <x:v>6,500字</x:v>
       </x:c>
       <x:c r="P49" s="16" t="n">
-        <x:v>8730</x:v>
+        <x:v>5525</x:v>
       </x:c>
       <x:c r="Q49" s="16" t="n">
-        <x:v>9270</x:v>
+        <x:v>8450</x:v>
       </x:c>
       <x:c r="R49" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; セキュリティプラグイン</x:v>
       </x:c>
       <x:c r="S49" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>セキュリティプラグイン、WAF・サーバー、マルウェア対策</x:v>
       </x:c>
       <x:c r="T49" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -4961,7 +4977,7 @@
         <x:v>019.png</x:v>
       </x:c>
       <x:c r="X49" s="14" t="str">
-        <x:v>Wordfenceの使い方と設定｜無料版でどこまで守れるか</x:v>
+        <x:v>Wordfence無料版の設定と機能範囲</x:v>
       </x:c>
       <x:c r="Y49" s="16" t="str">
         <x:v>未着手</x:v>
@@ -4975,15 +4991,15 @@
       <x:c r="AB49" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC49" s="16" t="str"/>
-      <x:c r="AD49" s="16" t="str"/>
-      <x:c r="AE49" s="16" t="str"/>
-      <x:c r="AF49" s="16" t="str"/>
-      <x:c r="AG49" s="16" t="str"/>
-      <x:c r="AH49" s="16" t="str"/>
-      <x:c r="AI49" s="16" t="str"/>
-      <x:c r="AJ49" s="14" t="str"/>
-      <x:c r="AK49" s="14" t="str"/>
+      <x:c r="AC49" s="16"/>
+      <x:c r="AD49" s="16"/>
+      <x:c r="AE49" s="16"/>
+      <x:c r="AF49" s="16"/>
+      <x:c r="AG49" s="16"/>
+      <x:c r="AH49" s="16"/>
+      <x:c r="AI49" s="16"/>
+      <x:c r="AJ49" s="14"/>
+      <x:c r="AK49" s="14"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="16" t="n">
@@ -4998,8 +5014,10 @@
       <x:c r="D50" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E50" s="14" t="str"/>
-      <x:c r="F50" s="14" t="str"/>
+      <x:c r="E50" s="14"/>
+      <x:c r="F50" s="14" t="str">
+        <x:v>BackWPup、UpdraftPlus、保存先、世代管理、復元テスト、自動バックアップ</x:v>
+      </x:c>
       <x:c r="G50" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5016,28 +5034,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L50" s="16" t="str">
-        <x:v>バックアップはセキュリティ対策｜BackWPup・UpdraftPlus比較と復旧手順</x:v>
+        <x:v>WordPressバックアップ比較｜復旧手順まで確認</x:v>
       </x:c>
       <x:c r="M50" s="16" t="str">
         <x:v>wordpress-backup-security</x:v>
       </x:c>
       <x:c r="N50" s="16" t="str">
-        <x:v>バックアップはセキュリティ対策をテーマに、BackWPup・UpdraftPlus比較と復旧手順ための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>BackWPupとUpdraftPlusを、保存先、実行頻度、世代管理、復元操作で比較します。WordPressのバックアップを取得するだけでなく、障害時に戻せる状態かを復元テストで確認できます。保管先の選び方も決められます。</x:v>
       </x:c>
       <x:c r="O50" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P50" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q50" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R50" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; サーバーと環境</x:v>
       </x:c>
       <x:c r="S50" s="14" t="str">
-        <x:v>WordPress、セキュリティ、バックアップ</x:v>
+        <x:v>バックアップ、インシデント対応、基本対策</x:v>
       </x:c>
       <x:c r="T50" s="14" t="str">
         <x:v>01,06,24</x:v>
@@ -5052,7 +5070,7 @@
         <x:v>021.png</x:v>
       </x:c>
       <x:c r="X50" s="14" t="str">
-        <x:v>バックアップはセキュリティ対策｜BackWPup・UpdraftPlus比較と復旧手順</x:v>
+        <x:v>WordPressバックアップ比較｜復旧手順まで確認</x:v>
       </x:c>
       <x:c r="Y50" s="16" t="str">
         <x:v>未着手</x:v>
@@ -5066,15 +5084,15 @@
       <x:c r="AB50" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC50" s="16" t="str"/>
-      <x:c r="AD50" s="16" t="str"/>
-      <x:c r="AE50" s="16" t="str"/>
-      <x:c r="AF50" s="16" t="str"/>
-      <x:c r="AG50" s="16" t="str"/>
-      <x:c r="AH50" s="16" t="str"/>
-      <x:c r="AI50" s="16" t="str"/>
-      <x:c r="AJ50" s="14" t="str"/>
-      <x:c r="AK50" s="14" t="str"/>
+      <x:c r="AC50" s="16"/>
+      <x:c r="AD50" s="16"/>
+      <x:c r="AE50" s="16"/>
+      <x:c r="AF50" s="16"/>
+      <x:c r="AG50" s="16"/>
+      <x:c r="AH50" s="16"/>
+      <x:c r="AI50" s="16"/>
+      <x:c r="AJ50" s="14"/>
+      <x:c r="AK50" s="14"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="16" t="n">
@@ -5089,8 +5107,10 @@
       <x:c r="D51" s="16" t="str">
         <x:v>弱</x:v>
       </x:c>
-      <x:c r="E51" s="14" t="str"/>
-      <x:c r="F51" s="14" t="str"/>
+      <x:c r="E51" s="14"/>
+      <x:c r="F51" s="14" t="str">
+        <x:v>WAF、セキュリティプラグイン、CDN、サーバー機能、重複、責任分界</x:v>
+      </x:c>
       <x:c r="G51" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -5107,28 +5127,28 @@
         <x:v>GEO</x:v>
       </x:c>
       <x:c r="L51" s="16" t="str">
-        <x:v>プラグイン・WAF・サーバー機能の役割分担｜どれをどこまで使うか</x:v>
+        <x:v>WordPress防御機能の役割分担｜WAFとプラグイン</x:v>
       </x:c>
       <x:c r="M51" s="16" t="str">
         <x:v>wordpress-security-roles</x:v>
       </x:c>
       <x:c r="N51" s="16" t="str">
-        <x:v>プラグイン・WAF・サーバー機能の役割分担をテーマに、どれをどこまで使うかための考え方と手順を実務目線で解説します。注意点と対応の優先順位も整理し、WordPress運用者が次に取るべき行動を具体的に示します。</x:v>
+        <x:v>WAF、セキュリティプラグイン、CDN、サーバー標準機能が守る範囲を比較します。同じ機能の重複や監視漏れを避け、WordPressの防御をどこへ配置するか判断できます。防御の抜けと重複を見直せます。点検表としても使えます。</x:v>
       </x:c>
       <x:c r="O51" s="16" t="str">
-        <x:v>8,000字</x:v>
+        <x:v>6,000字</x:v>
       </x:c>
       <x:c r="P51" s="16" t="n">
-        <x:v>7760</x:v>
+        <x:v>5100</x:v>
       </x:c>
       <x:c r="Q51" s="16" t="n">
-        <x:v>8240</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="R51" s="14" t="str">
-        <x:v>WordPressセキュリティ</x:v>
+        <x:v>WordPressセキュリティ &gt; 対策と設定</x:v>
       </x:c>
       <x:c r="S51" s="14" t="str">
-        <x:v>WordPress、セキュリティ、セキュリティプラグイン</x:v>
+        <x:v>WAF・サーバー、セキュリティプラグイン、基本対策</x:v>
       </x:c>
       <x:c r="T51" s="14" t="str">
         <x:v>01,40,46</x:v>
@@ -5143,7 +5163,7 @@
         <x:v>022.png</x:v>
       </x:c>
       <x:c r="X51" s="14" t="str">
-        <x:v>プラグイン・WAF・サーバー機能の役割分担｜どれをどこまで使うか</x:v>
+        <x:v>WordPress防御機能の役割分担｜WAFとプラグイン</x:v>
       </x:c>
       <x:c r="Y51" s="16" t="str">
         <x:v>未着手</x:v>
@@ -5157,15 +5177,15 @@
       <x:c r="AB51" s="16" t="str">
         <x:v>未投稿</x:v>
       </x:c>
-      <x:c r="AC51" s="16" t="str"/>
-      <x:c r="AD51" s="16" t="str"/>
-      <x:c r="AE51" s="16" t="str"/>
-      <x:c r="AF51" s="16" t="str"/>
-      <x:c r="AG51" s="16" t="str"/>
-      <x:c r="AH51" s="16" t="str"/>
-      <x:c r="AI51" s="16" t="str"/>
-      <x:c r="AJ51" s="14" t="str"/>
-      <x:c r="AK51" s="14" t="str"/>
+      <x:c r="AC51" s="16"/>
+      <x:c r="AD51" s="16"/>
+      <x:c r="AE51" s="16"/>
+      <x:c r="AF51" s="16"/>
+      <x:c r="AG51" s="16"/>
+      <x:c r="AH51" s="16"/>
+      <x:c r="AI51" s="16"/>
+      <x:c r="AJ51" s="14"/>
+      <x:c r="AK51" s="14"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="Y2:Y51">
@@ -10512,10 +10532,10 @@
         <x:v>文字数</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>設計書の文字数を基準とし、本文コア文字数は原則±3％以内。</x:v>
+        <x:v>制作管理表の文字数目安を基準とし、許容下限は目安×0.85、許容上限は目安×1.30。下限を埋めるための一般論や重複追加は行わず、検索意図を満たす情報密度を優先する。</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>品質検査CSVでOKを確認</x:v>
+        <x:v>本文文字数を実測して許容範囲と照合。範囲外の場合は不足論点または冗長箇所を確認し、単純な水増しで調整しない。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">

--- a/data/wordpress-security-production.xlsx
+++ b/data/wordpress-security-production.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="制作管理表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成共通プロンプト" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画像生成プロンプト一覧" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KWデータ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執筆・QAルール" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進捗サマリー" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="制作管理表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="画像生成共通プロンプト" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="画像生成プロンプト一覧" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KWデータ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執筆・QAルール" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="進捗サマリー" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -2360,22 +2360,36 @@
       </c>
       <c r="AA14" s="16" t="inlineStr">
         <is>
-          <t>画像未作成</t>
+          <t>要画像確認</t>
         </is>
       </c>
       <c r="AB14" s="16" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC14" s="16" t="n"/>
       <c r="AD14" s="16" t="n"/>
       <c r="AE14" s="16" t="n"/>
       <c r="AF14" s="16" t="n"/>
-      <c r="AG14" s="16" t="n"/>
-      <c r="AH14" s="16" t="n"/>
-      <c r="AI14" s="16" t="n"/>
-      <c r="AJ14" s="14" t="n"/>
+      <c r="AG14" s="16" t="inlineStr">
+        <is>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH14" s="16" t="n">
+        <v>7791</v>
+      </c>
+      <c r="AI14" s="16" t="inlineStr">
+        <is>
+          <t>不足(目安9,000字)</t>
+        </is>
+      </c>
+      <c r="AJ14" s="14" t="inlineStr">
+        <is>
+          <t>WordPress API エラー 400 term_exists: この項目の親項目の下に同じ名前のものがすでに存在しています。</t>
+        </is>
+      </c>
       <c r="AK14" s="14" t="n"/>
     </row>
     <row r="15">
@@ -2634,22 +2648,36 @@
       </c>
       <c r="AA16" s="16" t="inlineStr">
         <is>
-          <t>画像未作成</t>
+          <t>要画像確認</t>
         </is>
       </c>
       <c r="AB16" s="16" t="inlineStr">
         <is>
-          <t>未投稿</t>
+          <t>error</t>
         </is>
       </c>
       <c r="AC16" s="16" t="n"/>
       <c r="AD16" s="16" t="n"/>
       <c r="AE16" s="16" t="n"/>
       <c r="AF16" s="16" t="n"/>
-      <c r="AG16" s="16" t="n"/>
-      <c r="AH16" s="16" t="n"/>
-      <c r="AI16" s="16" t="n"/>
-      <c r="AJ16" s="14" t="n"/>
+      <c r="AG16" s="16" t="inlineStr">
+        <is>
+          <t>post/create_only</t>
+        </is>
+      </c>
+      <c r="AH16" s="16" t="n">
+        <v>6657</v>
+      </c>
+      <c r="AI16" s="16" t="inlineStr">
+        <is>
+          <t>不足(目安7,500字)</t>
+        </is>
+      </c>
+      <c r="AJ16" s="14" t="inlineStr">
+        <is>
+          <t>WordPress API エラー 400 term_exists: この項目の親項目の下に同じ名前のものがすでに存在しています。</t>
+        </is>
+      </c>
       <c r="AK16" s="14" t="n"/>
     </row>
     <row r="17">
